--- a/tame_output/ON/bt/strategyON_20240410.xlsx
+++ b/tame_output/ON/bt/strategyON_20240410.xlsx
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-521.3%</t>
+          <t>-521.0%</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-211.7%</t>
+          <t>-211.6%</t>
         </is>
       </c>
     </row>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>70.5%</t>
+          <t>70.6%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-18.8%</t>
+          <t>-18.7%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>58.7%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>40.1%</t>
+          <t>40.2%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-227.1%</t>
+          <t>-226.9%</t>
         </is>
       </c>
     </row>
@@ -1400,7 +1400,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.8%</t>
+          <t>-16.9%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-139.5%</t>
+          <t>-139.4%</t>
         </is>
       </c>
     </row>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096478</v>
+        <v>3.856158176096477</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761809</v>
+        <v>3.787326853761808</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
@@ -45918,16 +45918,16 @@
         <v>3.083932066077213</v>
       </c>
       <c r="D1929" t="n">
-        <v>-3.59699880637237</v>
+        <v>-3.594154588402602</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.644776119214518</v>
+        <v>1.645913806402425</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.031137158759456</v>
+        <v>-0.02949564679640915</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.06524977082154</v>
+        <v>3.066234677999368</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240410.xlsx
+++ b/tame_output/ON/bt/strategyON_20240410.xlsx
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-77.6%</t>
+          <t>-78.4%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>118.1%</t>
+          <t>117.8%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>97.8%</t>
+          <t>97.0%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>28.0%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-73.2%</t>
+          <t>-74.6%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>97.9%</t>
+          <t>97.7%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>499.3%</t>
+          <t>498.8%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-521.0%</t>
+          <t>-541.5%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>16.5%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.1%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>46.1%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>14.1%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>14.5%</t>
+          <t>12.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.1%</t>
+          <t>46.0%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-296.0%</t>
+          <t>-295.4%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-211.6%</t>
+          <t>-219.8%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-26.2%</t>
+          <t>-28.0%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>70.8%</t>
+          <t>70.6%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>70.6%</t>
+          <t>69.8%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>11.7%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-18.7%</t>
+          <t>-21.7%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>58.7%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>40.2%</t>
+          <t>31.4%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-226.9%</t>
+          <t>-240.9%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>55.1%</t>
+          <t>52.8%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>51.3%</t>
+          <t>51.2%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>41.8%</t>
+          <t>41.5%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>12.1%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1476,22 +1476,22 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>51.1%</t>
+          <t>47.8%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>42.8%</t>
+          <t>42.7%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.9%</t>
+          <t>-16.6%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-139.4%</t>
+          <t>-147.8%</t>
         </is>
       </c>
     </row>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341318</v>
+        <v>3.503170282341319</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407494</v>
+        <v>3.492445136407495</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199886</v>
+        <v>3.496848329199887</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910629</v>
+        <v>3.49996816391063</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078597</v>
+        <v>3.490055666078598</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.48587501888027</v>
+        <v>3.485875018880271</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234395</v>
+        <v>3.480688917234396</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860585</v>
+        <v>3.493712438860586</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767398</v>
+        <v>3.492098065767399</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792543</v>
+        <v>3.573670449792544</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.60003468962892</v>
+        <v>3.600034689628921</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410718</v>
+        <v>3.691568158410719</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240578</v>
+        <v>3.676837974240579</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282102</v>
+        <v>3.684840248282103</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116217</v>
+        <v>3.710931958116218</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.72857435442533</v>
+        <v>3.728574354425331</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702414</v>
+        <v>3.747699084702415</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906229</v>
+        <v>3.76631350390623</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096477</v>
+        <v>3.856158176096478</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761808</v>
+        <v>3.787326853761809</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
@@ -45918,16 +45918,16 @@
         <v>3.083932066077213</v>
       </c>
       <c r="D1929" t="n">
-        <v>-3.594154588402602</v>
+        <v>-3.799358772256716</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.645913806402425</v>
+        <v>1.563832132860779</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.02949564679640915</v>
+        <v>-0.1693253894028589</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.066234677999368</v>
+        <v>2.982336832435498</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240410.xlsx
+++ b/tame_output/ON/bt/strategyON_20240410.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>55.1%</t>
+          <t>66.0%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>53.4%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>67.7%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-19.5%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-17.5%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.7%</t>
+          <t>18.3%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.5%</t>
+          <t>-11.9%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>26.8%</t>
+          <t>57.0%</t>
         </is>
       </c>
     </row>
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>57.2%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>23.0%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.4%</t>
+          <t>-77.0%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>117.8%</t>
+          <t>117.7%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>137.2%</t>
+          <t>136.3%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>97.0%</t>
+          <t>97.9%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-694.2%</t>
+          <t>-684.8%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>28.0%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-55.6%</t>
+          <t>-55.2%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.6%</t>
+          <t>-72.5%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>97.7%</t>
+          <t>97.6%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>498.8%</t>
+          <t>502.0%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>6.1%</t>
+          <t>5.1%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-541.5%</t>
+          <t>-511.3%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>17.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>65.6%</t>
+          <t>65.3%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>46.1%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-272.3%</t>
+          <t>-268.5%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>14.1%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-43.4%</t>
+          <t>-43.1%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>12.1%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-295.4%</t>
+          <t>-86.2%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>38.2%</t>
+          <t>37.1%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-219.8%</t>
+          <t>-207.7%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-28.0%</t>
+          <t>-24.2%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>70.6%</t>
+          <t>70.0%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>71.0%</t>
+          <t>69.7%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>69.8%</t>
+          <t>70.6%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.7%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-36.0%</t>
+          <t>-35.4%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-21.7%</t>
+          <t>-16.7%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>58.7%</t>
+          <t>58.2%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>31.4%</t>
+          <t>32.6%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-154.0%</t>
+          <t>-168.7%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-240.9%</t>
+          <t>-217.5%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>52.8%</t>
+          <t>57.2%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>51.2%</t>
+          <t>50.9%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>62.7%</t>
+          <t>61.9%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>41.5%</t>
+          <t>41.8%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>97.4%</t>
+          <t>97.3%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.1%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-31.1%</t>
+          <t>-30.6%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>47.8%</t>
+          <t>51.5%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>42.7%</t>
+          <t>42.5%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.0%</t>
+          <t>34.3%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-147.8%</t>
+          <t>-133.8%</t>
         </is>
       </c>
     </row>
@@ -44624,22 +44624,22 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317621</v>
+        <v>3.447750501317622</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.553242699416938</v>
+        <v>-9.459405155904145</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.7060482391424867</v>
+        <v>-0.6685132217373693</v>
       </c>
       <c r="F1873" t="n">
-        <v>-2.072925655056207</v>
+        <v>-1.979088111543413</v>
       </c>
       <c r="G1873" t="n">
-        <v>1.871849871904312</v>
+        <v>1.928152398011989</v>
       </c>
     </row>
     <row r="1874">
@@ -44647,22 +44647,22 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737175</v>
+        <v>3.503515506737176</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.912773021920939</v>
+        <v>-9.818935478408147</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.8445100648460371</v>
+        <v>-0.8069750474409201</v>
       </c>
       <c r="F1874" t="n">
-        <v>-2.072925655056207</v>
+        <v>-1.979088111543413</v>
       </c>
       <c r="G1874" t="n">
-        <v>1.877200175202362</v>
+        <v>1.933502701310038</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-10.23917305058595</v>
+        <v>-10.14533550707316</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.9671540563548651</v>
+        <v>-0.9296190389497476</v>
       </c>
       <c r="F1875" t="n">
-        <v>-2.39932568372122</v>
+        <v>-2.305488140208426</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.689276177960532</v>
+        <v>1.745578704068208</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-10.23269690379239</v>
+        <v>-10.1388593602796</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.9615218470156717</v>
+        <v>-0.9239868296105551</v>
       </c>
       <c r="F1876" t="n">
-        <v>-2.39284953692766</v>
+        <v>-2.299011993414867</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.696203616658437</v>
+        <v>1.752506142766113</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.22900597883598</v>
+        <v>-10.13516843532319</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.9600454770331077</v>
+        <v>-0.9225104596279903</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.39284953692766</v>
+        <v>-2.299011993414867</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.696203616658437</v>
+        <v>1.752506142766113</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.43326415416585</v>
+        <v>-10.33942661065305</v>
       </c>
       <c r="E1878" t="n">
-        <v>-1.036235550046411</v>
+        <v>-0.9987005326412941</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.520488481541649</v>
+        <v>-2.426650938028855</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.625133447008686</v>
+        <v>1.681435973116362</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.59390318065421</v>
+        <v>-10.50006563714142</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.096008606157321</v>
+        <v>-1.058473588752204</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.635221954544045</v>
+        <v>-2.541384411031251</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.560775917691684</v>
+        <v>1.61707844379936</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.52043334898676</v>
+        <v>-10.42659580547397</v>
       </c>
       <c r="E1880" t="n">
-        <v>-1.05124897199692</v>
+        <v>-1.013713954591803</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.561752122876596</v>
+        <v>-2.467914579363803</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.620229518185575</v>
+        <v>1.676532044293251</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.69555776637331</v>
+        <v>-10.60172022286051</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.106743518204021</v>
+        <v>-1.069208500798903</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.73687654026314</v>
+        <v>-2.643038996750346</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.529710088501165</v>
+        <v>1.586012614608841</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.93000986038779</v>
+        <v>-10.836172316875</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.207743520711413</v>
+        <v>-1.170208503306295</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.73687654026314</v>
+        <v>-2.643038996750346</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.522490923599569</v>
+        <v>1.578793449707245</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-11.21781370492503</v>
+        <v>-11.12397616141224</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.329537249300284</v>
+        <v>-1.292002231895167</v>
       </c>
       <c r="F1883" t="n">
-        <v>-3.024680384800378</v>
+        <v>-2.930842841287585</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.34313642610325</v>
+        <v>1.399438952210926</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-11.44763815208886</v>
+        <v>-11.35380060857607</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.420351238327258</v>
+        <v>-1.382816220922141</v>
       </c>
       <c r="F1884" t="n">
-        <v>-3.187327921870539</v>
+        <v>-3.093490378357745</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.24666369369971</v>
+        <v>1.302966219807386</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-11.67966707182512</v>
+        <v>-11.58582952831233</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.510469077592648</v>
+        <v>-1.47293406018753</v>
       </c>
       <c r="F1885" t="n">
-        <v>-3.249340619058962</v>
+        <v>-3.155503075546168</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.212149804015771</v>
+        <v>1.268452330123447</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-11.62765155785631</v>
+        <v>-11.53381401434351</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.485672536318722</v>
+        <v>-1.448137518913605</v>
       </c>
       <c r="F1886" t="n">
-        <v>-3.249340619058962</v>
+        <v>-3.155503075546168</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.216140139702172</v>
+        <v>1.272442665809848</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-11.76932339958043</v>
+        <v>-11.67548585606763</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.543816499907112</v>
+        <v>-1.506281482501994</v>
       </c>
       <c r="F1887" t="n">
-        <v>-3.249340619058962</v>
+        <v>-3.155503075546168</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.21466491280343</v>
+        <v>1.270967438911106</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-11.8682301400397</v>
+        <v>-11.77439259652691</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.568325785925949</v>
+        <v>-1.530790768520833</v>
       </c>
       <c r="F1888" t="n">
-        <v>-3.348247359518238</v>
+        <v>-3.254409816005444</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.170374278692737</v>
+        <v>1.226676804800413</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-11.6690780328026</v>
+        <v>-11.57524048928981</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.501716076677793</v>
+        <v>-1.464181059272676</v>
       </c>
       <c r="F1889" t="n">
-        <v>-3.182924833568424</v>
+        <v>-3.089087290055631</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.256516660615942</v>
+        <v>1.312819186723618</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-11.44323288008319</v>
+        <v>-11.3493953365704</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.401798942553821</v>
+        <v>-1.364263925148702</v>
       </c>
       <c r="F1890" t="n">
-        <v>-3.140998157981261</v>
+        <v>-3.047160614468467</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.291251739004449</v>
+        <v>1.347554265112125</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.1569580677605</v>
+        <v>-11.0631205242477</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.286149873068684</v>
+        <v>-1.248614855663565</v>
       </c>
       <c r="F1891" t="n">
-        <v>-3.140998157981261</v>
+        <v>-3.047160614468467</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.292390883560508</v>
+        <v>1.348693409668184</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.20985335580479</v>
+        <v>-11.11601581229199</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.30467421412429</v>
+        <v>-1.267139196719173</v>
       </c>
       <c r="F1892" t="n">
-        <v>-3.136042811892815</v>
+        <v>-3.042205268380021</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.297997865375683</v>
+        <v>1.354300391483359</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.92594462487604</v>
+        <v>-10.83210708136324</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.185377017514154</v>
+        <v>-1.147842000109036</v>
       </c>
       <c r="F1893" t="n">
-        <v>-3.136042811892815</v>
+        <v>-3.042205268380021</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.303731569614319</v>
+        <v>1.360034095721995</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.67895737468309</v>
+        <v>-10.58511983117029</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.096319379830839</v>
+        <v>-1.058784362425721</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.889055561699863</v>
+        <v>-2.795218018187069</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.442186657336225</v>
+        <v>1.498489183443901</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.41512050747902</v>
+        <v>-10.32128296396622</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.000668114262119</v>
+        <v>-0.9631330968570011</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.889055561699863</v>
+        <v>-2.795218018187069</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.432303176023318</v>
+        <v>1.488605702130994</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.14787870661062</v>
+        <v>-10.05404116309782</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.8956059544141328</v>
+        <v>-0.8580709370090154</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.889055561699863</v>
+        <v>-2.795218018187069</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.430468615523944</v>
+        <v>1.48677114163162</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.872069543210133</v>
+        <v>-9.778231999697338</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.7855826040273999</v>
+        <v>-0.7480475866222824</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.800036253421129</v>
+        <v>-2.706198709908335</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.483579885517723</v>
+        <v>1.5398824116254</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.848116002234175</v>
+        <v>-9.75427845872138</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.7753326814915233</v>
+        <v>-0.7377976640864055</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.776082712445171</v>
+        <v>-2.682245168932378</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.498620516248791</v>
+        <v>1.554923042356467</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.584056063911378</v>
+        <v>-9.490218520398583</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.6829690223241567</v>
+        <v>-0.6454340049190388</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.512022774122376</v>
+        <v>-2.418185230609582</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.643796163080717</v>
+        <v>1.700098689188393</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.876976440406541</v>
+        <v>-8.783138896893746</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.4029242065825227</v>
+        <v>-0.3653891891774048</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.512022774122376</v>
+        <v>-2.418185230609582</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.641009129420416</v>
+        <v>1.697311655528092</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.83679214204035</v>
+        <v>-8.742954598527556</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.3865068633482052</v>
+        <v>-0.3489718459430873</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.471838475756185</v>
+        <v>-2.378000932243391</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.665463332327972</v>
+        <v>1.721765858435648</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.582250242699274</v>
+        <v>-8.48841269918648</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.2853232823910177</v>
+        <v>-0.2477882649858998</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.217296576415109</v>
+        <v>-2.123459032902316</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.817555293153374</v>
+        <v>1.87385781926105</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761809</v>
+        <v>3.78732685376181</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.348769020469675</v>
+        <v>-8.25493147695688</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.1840063646613257</v>
+        <v>-0.1464713472562078</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.983815354185511</v>
+        <v>-1.889977810672717</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.965568455328985</v>
+        <v>2.021870981436662</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255785</v>
+        <v>3.801633547255786</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.169060490325801</v>
+        <v>-8.075222946813007</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.1150151629167353</v>
+        <v>-0.07748014551161742</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.926643850022814</v>
+        <v>-1.832806306510021</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.996979147513644</v>
+        <v>2.05328167362132</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860427</v>
+        <v>3.763178672860429</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.036785016694914</v>
+        <v>-7.94294747318212</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.06673748671735336</v>
+        <v>-0.02920246931223591</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.794368376391928</v>
+        <v>-1.700530832879134</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.071711918439203</v>
+        <v>2.12801444454688</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575953</v>
+        <v>3.784715218575955</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.846185342021761</v>
+        <v>-7.752347798508968</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.01231744383954414</v>
+        <v>0.04985246124466158</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.603768701718775</v>
+        <v>-1.509931158205981</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.188886783930732</v>
+        <v>2.245189310038408</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430988</v>
+        <v>3.75387899643099</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.59718554333818</v>
+        <v>-7.503347999825387</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.1248237045366354</v>
+        <v>0.1623587219417528</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.603768701718775</v>
+        <v>-1.509931158205981</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.20179312515439</v>
+        <v>2.258095651262066</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077645</v>
+        <v>3.692928280077647</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.702775533111285</v>
+        <v>-7.608937989598491</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.04538822097182482</v>
+        <v>-0.007853203566707379</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.709358691491879</v>
+        <v>-1.615521147979086</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.010463201691309</v>
+        <v>2.066765727798985</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457903</v>
+        <v>3.770419008457905</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.721510435229882</v>
+        <v>-7.627672891717088</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.004337839942177624</v>
+        <v>0.03319717746293982</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.709358691491879</v>
+        <v>-1.615521147979086</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.059007543568395</v>
+        <v>2.115310069676072</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180809</v>
+        <v>3.760330111180811</v>
       </c>
       <c r="C1910" t="n">
         <v>3.088001770449517</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.44477226055907</v>
+        <v>-7.350934717046275</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.1097364419121418</v>
+        <v>0.1472714593172597</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.527542030381953</v>
+        <v>-1.43370448686916</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.171476552220346</v>
+        <v>2.227779078328022</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879203</v>
+        <v>3.723562653879204</v>
       </c>
       <c r="C1911" t="n">
         <v>3.079287784196039</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.317879854124</v>
+        <v>-7.224042310611205</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.1517794182326919</v>
+        <v>0.1893144356378098</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.400649623946884</v>
+        <v>-1.30681208043409</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.238898009827909</v>
+        <v>2.295200535935586</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568107</v>
+        <v>3.729966140568108</v>
       </c>
       <c r="C1912" t="n">
         <v>3.072327172100946</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.130292346214073</v>
+        <v>-7.036454802701279</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.2198538093015694</v>
+        <v>0.2573888267066873</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.400649623946884</v>
+        <v>-1.30681208043409</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.231937397732816</v>
+        <v>2.288239923840492</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963418</v>
+        <v>3.78291895796342</v>
       </c>
       <c r="C1913" t="n">
         <v>3.086789526482089</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.888143952760215</v>
+        <v>-6.794306409247421</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.3311755210642557</v>
+        <v>0.3687105384693736</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.400649623946884</v>
+        <v>-1.30681208043409</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.246399752113959</v>
+        <v>2.302702278221636</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192817</v>
+        <v>3.828547911192818</v>
       </c>
       <c r="C1914" t="n">
         <v>3.081321646941284</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.824914580991867</v>
+        <v>-6.731077037479072</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.3509993902307902</v>
+        <v>0.3885344076359076</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.400649623946884</v>
+        <v>-1.30681208043409</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.240931872573154</v>
+        <v>2.297234398680831</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262047</v>
+        <v>3.828049353262049</v>
       </c>
       <c r="C1915" t="n">
         <v>3.078819740951861</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.638426888614861</v>
+        <v>-6.544589345102066</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.4230925611921692</v>
+        <v>0.4606275785972871</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.214161931569877</v>
+        <v>-1.120324388057084</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.350322582009935</v>
+        <v>2.406625108117611</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389909</v>
+        <v>3.812450103389911</v>
       </c>
       <c r="C1916" t="n">
         <v>3.086520719189187</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.617277689711417</v>
+        <v>-6.523440146198623</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.4392532189908724</v>
+        <v>0.4767882363959899</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.193012732666434</v>
+        <v>-1.09917518915364</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.370713079589327</v>
+        <v>2.427015605697003</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788095</v>
+        <v>3.748324832788096</v>
       </c>
       <c r="C1917" t="n">
         <v>3.082301427536237</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.373512247727973</v>
+        <v>-6.279674704215179</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.5325401041313005</v>
+        <v>0.5700751215364184</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.193012732666434</v>
+        <v>-1.09917518915364</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.366493787936377</v>
+        <v>2.422796314044053</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527526</v>
+        <v>3.824307657527528</v>
       </c>
       <c r="C1918" t="n">
         <v>3.084425741456253</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.109484180534713</v>
+        <v>-6.015646637021918</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.6402756449286207</v>
+        <v>0.6778106623337385</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.9911473338504804</v>
+        <v>-0.8973097903376868</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.489737341145966</v>
+        <v>2.546039867253642</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749185</v>
+        <v>3.826351398749186</v>
       </c>
       <c r="C1919" t="n">
         <v>3.077167816439955</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.859633786585638</v>
+        <v>-5.765796243072844</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.7329578774919527</v>
+        <v>0.7704928948970706</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.9911473338504804</v>
+        <v>-0.8973097903376868</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.482479416129667</v>
+        <v>2.538781942237343</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481498</v>
+        <v>3.8359544114815</v>
       </c>
       <c r="C1920" t="n">
         <v>3.080766939960604</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.556066297581659</v>
+        <v>-5.462228754068865</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.8579839966141933</v>
+        <v>0.8955190140193108</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.9911473338504804</v>
+        <v>-0.8973097903376868</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.486078539650316</v>
+        <v>2.542381065757993</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862987</v>
+        <v>3.780930335862989</v>
       </c>
       <c r="C1921" t="n">
         <v>3.094094446015158</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.482586388729645</v>
+        <v>-5.388748845216851</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.9007034662095523</v>
+        <v>0.9382384836146702</v>
       </c>
       <c r="F1921" t="n">
-        <v>-0.917667424998466</v>
+        <v>-0.8238298814856724</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.543493991016079</v>
+        <v>2.599796517123755</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102782</v>
+        <v>3.773761647102784</v>
       </c>
       <c r="C1922" t="n">
         <v>3.093114923631455</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.257553389060822</v>
+        <v>-5.163715845548028</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.9897371436933784</v>
+        <v>1.027272161098496</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.6926344253296431</v>
+        <v>-0.5987968818168495</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.677534268433669</v>
+        <v>2.733836794541345</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353077</v>
+        <v>3.764614304353079</v>
       </c>
       <c r="C1923" t="n">
         <v>3.097809724685772</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.042919011424416</v>
+        <v>-4.949081467911621</v>
       </c>
       <c r="E1923" t="n">
-        <v>1.080285695802258</v>
+        <v>1.117820713207376</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.4780000476932363</v>
+        <v>-0.3841625041804427</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.811009696069831</v>
+        <v>2.867312222177507</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544785</v>
+        <v>3.798811195544786</v>
       </c>
       <c r="C1924" t="n">
         <v>3.079003983469568</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.776318654450064</v>
+        <v>-4.682481110937269</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.168120097375795</v>
+        <v>1.205655114780913</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.4780000476932363</v>
+        <v>-0.3841625041804427</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.792203954853626</v>
+        <v>2.848506480961302</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712296</v>
+        <v>3.797691308712298</v>
       </c>
       <c r="C1925" t="n">
         <v>3.080747060094445</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.535888157645203</v>
+        <v>-4.442050614132409</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.266035372722616</v>
+        <v>1.303570390127734</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.2375695508883761</v>
+        <v>-0.1437320073755824</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.93820532956142</v>
+        <v>2.994507855669096</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837688</v>
+        <v>3.821589933837689</v>
       </c>
       <c r="C1926" t="n">
         <v>3.084676373929265</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.293097349995758</v>
+        <v>-4.199259806482964</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.367081009617215</v>
+        <v>1.404616027022333</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.2375695508883761</v>
+        <v>-0.1437320073755824</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.94213464339624</v>
+        <v>2.998437169503916</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822323422349969</v>
+        <v>3.822323422349971</v>
       </c>
       <c r="C1927" t="n">
         <v>3.085354957846605</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.053492258388669</v>
+        <v>-3.959654714875874</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.46360163017739</v>
+        <v>1.501136647582508</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.1705216032198815</v>
+        <v>-0.07668405970708791</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.983041995914677</v>
+        <v>3.039344522022353</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848613050972343</v>
+        <v>3.848613050972345</v>
       </c>
       <c r="C1928" t="n">
         <v>3.082353029066599</v>
       </c>
       <c r="D1928" t="n">
-        <v>-3.810836669965506</v>
+        <v>-3.716999126452711</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.557661936766649</v>
+        <v>1.595196954171767</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.1705216032198815</v>
+        <v>-0.07668405970708791</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.98004006713467</v>
+        <v>3.036342593242346</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.548862472309231</v>
+        <v>3.850955759817124</v>
       </c>
       <c r="C1929" t="n">
         <v>3.083932066077213</v>
       </c>
       <c r="D1929" t="n">
-        <v>-3.799358772256716</v>
+        <v>-3.4969783284157</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.563832132860779</v>
+        <v>1.684784310397186</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.1693253894028589</v>
+        <v>0.06453578536089233</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.982336832435498</v>
+        <v>3.122653537293749</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240410.xlsx
+++ b/tame_output/ON/bt/strategyON_20240410.xlsx
@@ -600,26 +600,26 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>66.0%</t>
+          <t>55.1%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>67.2%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,12 +628,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-04-09</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>67.3%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.5%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-17.5%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.3%</t>
+          <t>18.7%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.9%</t>
+          <t>-12.5%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>57.0%</t>
+          <t>26.0%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>71.9%</t>
+          <t>64.1%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>28.8%</t>
+          <t>30.3%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,12 +786,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-04-09</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>30.8%</t>
+          <t>34.1%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -801,45 +801,45 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>15.5%</t>
+          <t>30.1%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2021-03-21</t>
+          <t>2024-03-04</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2021-03-24</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-11.3%</t>
+          <t>-21.5%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-3.5%</t>
+          <t>-6.0%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.2%</t>
+          <t>-2.3%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-3.5%</t>
+          <t>-4.9%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>57.2%</t>
+          <t>49.3%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>23.0%</t>
+          <t>23.9%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-5.0%</t>
+          <t>-4.2%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-3.2%</t>
+          <t>-25.0%</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-77.0%</t>
+          <t>-78.4%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -926,7 +926,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,17 +944,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-04-09</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>136.3%</t>
+          <t>137.1%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>97.9%</t>
+          <t>97.0%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -973,11 +973,11 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-684.8%</t>
+          <t>-694.2%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>28.0%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-55.2%</t>
+          <t>-55.6%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-72.5%</t>
+          <t>-74.6%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>97.6%</t>
+          <t>97.7%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>502.0%</t>
+          <t>498.7%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>5.1%</t>
+          <t>6.1%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-511.3%</t>
+          <t>-541.5%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>17.5%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,17 +1102,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-04-09</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>65.3%</t>
+          <t>65.5%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>46.1%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1131,11 +1131,11 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-268.5%</t>
+          <t>-272.3%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>14.1%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-43.1%</t>
+          <t>-43.4%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>12.0%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-86.2%</t>
+          <t>-295.3%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>37.1%</t>
+          <t>38.2%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-207.7%</t>
+          <t>-219.8%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-24.2%</t>
+          <t>-28.0%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>70.0%</t>
+          <t>70.6%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,17 +1260,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-04-09</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>69.7%</t>
+          <t>70.9%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>70.6%</t>
+          <t>69.8%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>11.7%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-35.4%</t>
+          <t>-36.0%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-16.7%</t>
+          <t>-21.7%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>58.2%</t>
+          <t>58.6%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>32.6%</t>
+          <t>31.4%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-168.7%</t>
+          <t>-154.0%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-217.5%</t>
+          <t>-240.9%</t>
         </is>
       </c>
     </row>
@@ -1390,26 +1390,26 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>57.2%</t>
+          <t>49.0%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>50.9%</t>
+          <t>51.4%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.2%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,22 +1418,22 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-04-09</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>61.9%</t>
+          <t>63.2%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>41.8%</t>
+          <t>41.5%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>97.3%</t>
+          <t>97.4%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-30.6%</t>
+          <t>-31.1%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>51.5%</t>
+          <t>42.8%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>42.5%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.6%</t>
+          <t>-16.1%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.3%</t>
+          <t>34.0%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-133.8%</t>
+          <t>-160.1%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1929"/>
+  <dimension ref="A1:G1930"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297755</v>
+        <v>3.458100091297756</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.459405155904145</v>
+        <v>-9.553242699416938</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.6685132217373693</v>
+        <v>-0.7060482391424867</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.979088111543413</v>
+        <v>-2.072925655056207</v>
       </c>
       <c r="G1873" t="n">
-        <v>1.928152398011989</v>
+        <v>1.871849871904312</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.818935478408147</v>
+        <v>-9.912773021920939</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.8069750474409201</v>
+        <v>-0.8445100648460371</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.979088111543413</v>
+        <v>-2.072925655056207</v>
       </c>
       <c r="G1874" t="n">
-        <v>1.933502701310038</v>
+        <v>1.877200175202362</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-10.14533550707316</v>
+        <v>-10.23917305058595</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.9296190389497476</v>
+        <v>-0.9671540563548651</v>
       </c>
       <c r="F1875" t="n">
-        <v>-2.305488140208426</v>
+        <v>-2.39932568372122</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.745578704068208</v>
+        <v>1.689276177960532</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-10.1388593602796</v>
+        <v>-10.23269690379239</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.9239868296105551</v>
+        <v>-0.9615218470156717</v>
       </c>
       <c r="F1876" t="n">
-        <v>-2.299011993414867</v>
+        <v>-2.39284953692766</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.752506142766113</v>
+        <v>1.696203616658437</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.13516843532319</v>
+        <v>-10.22900597883598</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.9225104596279903</v>
+        <v>-0.9600454770331077</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.299011993414867</v>
+        <v>-2.39284953692766</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.752506142766113</v>
+        <v>1.696203616658437</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.33942661065305</v>
+        <v>-10.43326415416585</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.9987005326412941</v>
+        <v>-1.036235550046411</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.426650938028855</v>
+        <v>-2.520488481541649</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.681435973116362</v>
+        <v>1.625133447008686</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.50006563714142</v>
+        <v>-10.59390318065421</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.058473588752204</v>
+        <v>-1.096008606157321</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.541384411031251</v>
+        <v>-2.635221954544045</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.61707844379936</v>
+        <v>1.560775917691684</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.42659580547397</v>
+        <v>-10.52043334898676</v>
       </c>
       <c r="E1880" t="n">
-        <v>-1.013713954591803</v>
+        <v>-1.05124897199692</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.467914579363803</v>
+        <v>-2.561752122876596</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.676532044293251</v>
+        <v>1.620229518185575</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.60172022286051</v>
+        <v>-10.69555776637331</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.069208500798903</v>
+        <v>-1.106743518204021</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.643038996750346</v>
+        <v>-2.73687654026314</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.586012614608841</v>
+        <v>1.529710088501165</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.836172316875</v>
+        <v>-10.93000986038779</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.170208503306295</v>
+        <v>-1.207743520711413</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.643038996750346</v>
+        <v>-2.73687654026314</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.578793449707245</v>
+        <v>1.522490923599569</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-11.12397616141224</v>
+        <v>-11.21781370492503</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.292002231895167</v>
+        <v>-1.329537249300284</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.930842841287585</v>
+        <v>-3.024680384800378</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.399438952210926</v>
+        <v>1.34313642610325</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-11.35380060857607</v>
+        <v>-11.44763815208886</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.382816220922141</v>
+        <v>-1.420351238327258</v>
       </c>
       <c r="F1884" t="n">
-        <v>-3.093490378357745</v>
+        <v>-3.187327921870539</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.302966219807386</v>
+        <v>1.24666369369971</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-11.58582952831233</v>
+        <v>-11.67966707182512</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.47293406018753</v>
+        <v>-1.510469077592648</v>
       </c>
       <c r="F1885" t="n">
-        <v>-3.155503075546168</v>
+        <v>-3.249340619058962</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.268452330123447</v>
+        <v>1.212149804015771</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-11.53381401434351</v>
+        <v>-11.62765155785631</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.448137518913605</v>
+        <v>-1.485672536318722</v>
       </c>
       <c r="F1886" t="n">
-        <v>-3.155503075546168</v>
+        <v>-3.249340619058962</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.272442665809848</v>
+        <v>1.216140139702172</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-11.67548585606763</v>
+        <v>-11.76932339958043</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.506281482501994</v>
+        <v>-1.543816499907112</v>
       </c>
       <c r="F1887" t="n">
-        <v>-3.155503075546168</v>
+        <v>-3.249340619058962</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.270967438911106</v>
+        <v>1.21466491280343</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-11.77439259652691</v>
+        <v>-11.8682301400397</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.530790768520833</v>
+        <v>-1.568325785925949</v>
       </c>
       <c r="F1888" t="n">
-        <v>-3.254409816005444</v>
+        <v>-3.348247359518238</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.226676804800413</v>
+        <v>1.170374278692737</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-11.57524048928981</v>
+        <v>-11.6690780328026</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.464181059272676</v>
+        <v>-1.501716076677793</v>
       </c>
       <c r="F1889" t="n">
-        <v>-3.089087290055631</v>
+        <v>-3.182924833568424</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.312819186723618</v>
+        <v>1.256516660615942</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-11.3493953365704</v>
+        <v>-11.44323288008319</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.364263925148702</v>
+        <v>-1.401798942553821</v>
       </c>
       <c r="F1890" t="n">
-        <v>-3.047160614468467</v>
+        <v>-3.140998157981261</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.347554265112125</v>
+        <v>1.291251739004449</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.0631205242477</v>
+        <v>-11.1569580677605</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.248614855663565</v>
+        <v>-1.286149873068684</v>
       </c>
       <c r="F1891" t="n">
-        <v>-3.047160614468467</v>
+        <v>-3.140998157981261</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.348693409668184</v>
+        <v>1.292390883560508</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.11601581229199</v>
+        <v>-11.20985335580479</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.267139196719173</v>
+        <v>-1.30467421412429</v>
       </c>
       <c r="F1892" t="n">
-        <v>-3.042205268380021</v>
+        <v>-3.136042811892815</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.354300391483359</v>
+        <v>1.297997865375683</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.83210708136324</v>
+        <v>-10.92594462487604</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.147842000109036</v>
+        <v>-1.185377017514154</v>
       </c>
       <c r="F1893" t="n">
-        <v>-3.042205268380021</v>
+        <v>-3.136042811892815</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.360034095721995</v>
+        <v>1.303731569614319</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.58511983117029</v>
+        <v>-10.67895737468309</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.058784362425721</v>
+        <v>-1.096319379830839</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.795218018187069</v>
+        <v>-2.889055561699863</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.498489183443901</v>
+        <v>1.442186657336225</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.32128296396622</v>
+        <v>-10.41512050747902</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.9631330968570011</v>
+        <v>-1.000668114262119</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.795218018187069</v>
+        <v>-2.889055561699863</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.488605702130994</v>
+        <v>1.432303176023318</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.05404116309782</v>
+        <v>-10.14787870661062</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.8580709370090154</v>
+        <v>-0.8956059544141328</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.795218018187069</v>
+        <v>-2.889055561699863</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.48677114163162</v>
+        <v>1.430468615523944</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.778231999697338</v>
+        <v>-9.872069543210133</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.7480475866222824</v>
+        <v>-0.7855826040273999</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.706198709908335</v>
+        <v>-2.800036253421129</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.5398824116254</v>
+        <v>1.483579885517723</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.75427845872138</v>
+        <v>-9.848116002234175</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.7377976640864055</v>
+        <v>-0.7753326814915233</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.682245168932378</v>
+        <v>-2.776082712445171</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.554923042356467</v>
+        <v>1.498620516248791</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.490218520398583</v>
+        <v>-9.584056063911378</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.6454340049190388</v>
+        <v>-0.6829690223241567</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.418185230609582</v>
+        <v>-2.512022774122376</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.700098689188393</v>
+        <v>1.643796163080717</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.783138896893746</v>
+        <v>-8.876976440406541</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.3653891891774048</v>
+        <v>-0.4029242065825227</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.418185230609582</v>
+        <v>-2.512022774122376</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.697311655528092</v>
+        <v>1.641009129420416</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.742954598527556</v>
+        <v>-8.83679214204035</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.3489718459430873</v>
+        <v>-0.3865068633482052</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.378000932243391</v>
+        <v>-2.471838475756185</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.721765858435648</v>
+        <v>1.665463332327972</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.48841269918648</v>
+        <v>-8.582250242699274</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.2477882649858998</v>
+        <v>-0.2853232823910177</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.123459032902316</v>
+        <v>-2.217296576415109</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.87385781926105</v>
+        <v>1.817555293153374</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.25493147695688</v>
+        <v>-8.348769020469675</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.1464713472562078</v>
+        <v>-0.1840063646613257</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.889977810672717</v>
+        <v>-1.983815354185511</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.021870981436662</v>
+        <v>1.965568455328985</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.075222946813007</v>
+        <v>-8.169060490325801</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.07748014551161742</v>
+        <v>-0.1150151629167353</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.832806306510021</v>
+        <v>-1.926643850022814</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.05328167362132</v>
+        <v>1.996979147513644</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-7.94294747318212</v>
+        <v>-8.036785016694914</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.02920246931223591</v>
+        <v>-0.06673748671735336</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.700530832879134</v>
+        <v>-1.794368376391928</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.12801444454688</v>
+        <v>2.071711918439203</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.752347798508968</v>
+        <v>-7.846185342021761</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.04985246124466158</v>
+        <v>0.01231744383954414</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.509931158205981</v>
+        <v>-1.603768701718775</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.245189310038408</v>
+        <v>2.188886783930732</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.503347999825387</v>
+        <v>-7.59718554333818</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.1623587219417528</v>
+        <v>0.1248237045366354</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.509931158205981</v>
+        <v>-1.603768701718775</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.258095651262066</v>
+        <v>2.20179312515439</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.608937989598491</v>
+        <v>-7.702775533111285</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.007853203566707379</v>
+        <v>-0.04538822097182482</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.615521147979086</v>
+        <v>-1.709358691491879</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.066765727798985</v>
+        <v>2.010463201691309</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.627672891717088</v>
+        <v>-7.721510435229882</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.03319717746293982</v>
+        <v>-0.004337839942177624</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.615521147979086</v>
+        <v>-1.709358691491879</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.115310069676072</v>
+        <v>2.059007543568395</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>3.088001770449517</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.350934717046275</v>
+        <v>-7.44477226055907</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.1472714593172597</v>
+        <v>0.1097364419121418</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.43370448686916</v>
+        <v>-1.527542030381953</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.227779078328022</v>
+        <v>2.171476552220346</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>3.079287784196039</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.224042310611205</v>
+        <v>-7.317879854124</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.1893144356378098</v>
+        <v>0.1517794182326919</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.30681208043409</v>
+        <v>-1.400649623946884</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.295200535935586</v>
+        <v>2.238898009827909</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>3.072327172100946</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.036454802701279</v>
+        <v>-7.130292346214073</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.2573888267066873</v>
+        <v>0.2198538093015694</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.30681208043409</v>
+        <v>-1.400649623946884</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.288239923840492</v>
+        <v>2.231937397732816</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>3.086789526482089</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.794306409247421</v>
+        <v>-6.888143952760215</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.3687105384693736</v>
+        <v>0.3311755210642557</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.30681208043409</v>
+        <v>-1.400649623946884</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.302702278221636</v>
+        <v>2.246399752113959</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>3.081321646941284</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.731077037479072</v>
+        <v>-6.824914580991867</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.3885344076359076</v>
+        <v>0.3509993902307902</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.30681208043409</v>
+        <v>-1.400649623946884</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.297234398680831</v>
+        <v>2.240931872573154</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>3.078819740951861</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.544589345102066</v>
+        <v>-6.638426888614861</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.4606275785972871</v>
+        <v>0.4230925611921692</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.120324388057084</v>
+        <v>-1.214161931569877</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.406625108117611</v>
+        <v>2.350322582009935</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>3.086520719189187</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.523440146198623</v>
+        <v>-6.617277689711417</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.4767882363959899</v>
+        <v>0.4392532189908724</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.09917518915364</v>
+        <v>-1.193012732666434</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.427015605697003</v>
+        <v>2.370713079589327</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>3.082301427536237</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.279674704215179</v>
+        <v>-6.373512247727973</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.5700751215364184</v>
+        <v>0.5325401041313005</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.09917518915364</v>
+        <v>-1.193012732666434</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.422796314044053</v>
+        <v>2.366493787936377</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>3.084425741456253</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.015646637021918</v>
+        <v>-6.109484180534713</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.6778106623337385</v>
+        <v>0.6402756449286207</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.8973097903376868</v>
+        <v>-0.9911473338504804</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.546039867253642</v>
+        <v>2.489737341145966</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>3.077167816439955</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.765796243072844</v>
+        <v>-5.859633786585638</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.7704928948970706</v>
+        <v>0.7329578774919527</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.8973097903376868</v>
+        <v>-0.9911473338504804</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.538781942237343</v>
+        <v>2.482479416129667</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>3.080766939960604</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.462228754068865</v>
+        <v>-5.556066297581659</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.8955190140193108</v>
+        <v>0.8579839966141933</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.8973097903376868</v>
+        <v>-0.9911473338504804</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.542381065757993</v>
+        <v>2.486078539650316</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>3.094094446015158</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.388748845216851</v>
+        <v>-5.482586388729645</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.9382384836146702</v>
+        <v>0.9007034662095523</v>
       </c>
       <c r="F1921" t="n">
-        <v>-0.8238298814856724</v>
+        <v>-0.917667424998466</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.599796517123755</v>
+        <v>2.543493991016079</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>3.093114923631455</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.163715845548028</v>
+        <v>-5.257553389060822</v>
       </c>
       <c r="E1922" t="n">
-        <v>1.027272161098496</v>
+        <v>0.9897371436933784</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.5987968818168495</v>
+        <v>-0.6926344253296431</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.733836794541345</v>
+        <v>2.677534268433669</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>3.097809724685772</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.949081467911621</v>
+        <v>-5.042919011424416</v>
       </c>
       <c r="E1923" t="n">
-        <v>1.117820713207376</v>
+        <v>1.080285695802258</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.3841625041804427</v>
+        <v>-0.4780000476932363</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.867312222177507</v>
+        <v>2.811009696069831</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>3.079003983469568</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.682481110937269</v>
+        <v>-4.776318654450064</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.205655114780913</v>
+        <v>1.168120097375795</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.3841625041804427</v>
+        <v>-0.4780000476932363</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.848506480961302</v>
+        <v>2.792203954853626</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>3.080747060094445</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.442050614132409</v>
+        <v>-4.535888157645203</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.303570390127734</v>
+        <v>1.266035372722616</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.1437320073755824</v>
+        <v>-0.2375695508883761</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.994507855669096</v>
+        <v>2.93820532956142</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>3.084676373929265</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.199259806482964</v>
+        <v>-4.293097349995758</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.404616027022333</v>
+        <v>1.367081009617215</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.1437320073755824</v>
+        <v>-0.2375695508883761</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.998437169503916</v>
+        <v>2.94213464339624</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>3.085354957846605</v>
       </c>
       <c r="D1927" t="n">
-        <v>-3.959654714875874</v>
+        <v>-4.053492258388669</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.501136647582508</v>
+        <v>1.46360163017739</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.07668405970708791</v>
+        <v>-0.1705216032198815</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.039344522022353</v>
+        <v>2.983041995914677</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>3.082353029066599</v>
       </c>
       <c r="D1928" t="n">
-        <v>-3.716999126452711</v>
+        <v>-3.810836669965506</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.595196954171767</v>
+        <v>1.557661936766649</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.07668405970708791</v>
+        <v>-0.1705216032198815</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.036342593242346</v>
+        <v>2.98004006713467</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,45 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.850955759817124</v>
+        <v>3.818665376145945</v>
       </c>
       <c r="C1929" t="n">
         <v>3.083932066077213</v>
       </c>
       <c r="D1929" t="n">
-        <v>-3.4969783284157</v>
+        <v>-3.799358772256716</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.684784310397186</v>
+        <v>1.563832132860779</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.06453578536089233</v>
+        <v>-0.1693253894028589</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.122653537293749</v>
+        <v>2.982336832435498</v>
+      </c>
+    </row>
+    <row r="1930">
+      <c r="A1930" s="2" t="n">
+        <v>45392</v>
+      </c>
+      <c r="B1930" t="n">
+        <v>3.540533056027617</v>
+      </c>
+      <c r="C1930" t="n">
+        <v>2.866109101754391</v>
+      </c>
+      <c r="D1930" t="n">
+        <v>-3.799358772256716</v>
+      </c>
+      <c r="E1930" t="n">
+        <v>1.563832132860779</v>
+      </c>
+      <c r="F1930" t="n">
+        <v>-0.1693253894028589</v>
+      </c>
+      <c r="G1930" t="n">
+        <v>2.859172898740759</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240410.xlsx
+++ b/tame_output/ON/bt/strategyON_20240410.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>55.1%</t>
+          <t>66.0%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.2%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-19.5%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-17.5%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.7%</t>
+          <t>18.3%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.5%</t>
+          <t>-11.9%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>26.0%</t>
+          <t>57.1%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>64.1%</t>
+          <t>74.9%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>30.3%</t>
+          <t>29.1%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,45 +791,45 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>34.1%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>27.6%</t>
+          <t>28.1%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>30.1%</t>
+          <t>15.5%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2024-03-04</t>
+          <t>2021-03-21</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2021-03-24</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-21.5%</t>
+          <t>-11.3%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-6.0%</t>
+          <t>-3.5%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.3%</t>
+          <t>-2.2%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-4.9%</t>
+          <t>-3.5%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>49.3%</t>
+          <t>59.8%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>23.9%</t>
+          <t>23.3%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.2%</t>
+          <t>-5.0%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.1%</t>
+          <t>39.4%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-25.0%</t>
+          <t>6.4%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.4%</t>
+          <t>-77.7%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>117.7%</t>
+          <t>117.2%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>137.1%</t>
+          <t>136.1%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-694.2%</t>
+          <t>-683.5%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-55.6%</t>
+          <t>-55.2%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.6%</t>
+          <t>-73.4%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>97.7%</t>
+          <t>97.2%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>498.7%</t>
+          <t>502.0%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>6.1%</t>
+          <t>5.5%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-541.5%</t>
+          <t>-530.8%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>15.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>65.2%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-272.3%</t>
+          <t>-268.0%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-43.4%</t>
+          <t>-43.1%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.0%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-295.3%</t>
+          <t>-79.7%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>38.2%</t>
+          <t>36.4%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-219.8%</t>
+          <t>-215.6%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-28.0%</t>
+          <t>-25.8%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>70.6%</t>
+          <t>69.7%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>70.9%</t>
+          <t>69.6%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-36.0%</t>
+          <t>-35.4%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-21.7%</t>
+          <t>-18.4%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>58.6%</t>
+          <t>57.8%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>31.4%</t>
+          <t>32.8%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-154.0%</t>
+          <t>-154.7%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-240.9%</t>
+          <t>-230.3%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>49.0%</t>
+          <t>58.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>51.4%</t>
+          <t>51.0%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>59.2%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.2%</t>
+          <t>61.8%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>41.5%</t>
+          <t>42.1%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>97.4%</t>
+          <t>97.2%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-31.1%</t>
+          <t>-30.5%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>42.8%</t>
+          <t>52.7%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>42.5%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.1%</t>
+          <t>-16.6%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.0%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-160.1%</t>
+          <t>-128.7%</t>
         </is>
       </c>
     </row>
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.553242699416938</v>
+        <v>-9.446581082799119</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.7060482391424867</v>
+        <v>-0.6633835924953591</v>
       </c>
       <c r="F1873" t="n">
-        <v>-2.072925655056207</v>
+        <v>-1.966264038438387</v>
       </c>
       <c r="G1873" t="n">
-        <v>1.871849871904312</v>
+        <v>1.935846841875004</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.912773021920939</v>
+        <v>-9.80611140530312</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.8445100648460371</v>
+        <v>-0.8018454181989094</v>
       </c>
       <c r="F1874" t="n">
-        <v>-2.072925655056207</v>
+        <v>-1.966264038438387</v>
       </c>
       <c r="G1874" t="n">
-        <v>1.877200175202362</v>
+        <v>1.941197145173054</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-10.23917305058595</v>
+        <v>-10.13251143396813</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.9671540563548651</v>
+        <v>-0.924489409707737</v>
       </c>
       <c r="F1875" t="n">
-        <v>-2.39932568372122</v>
+        <v>-2.2926640671034</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.689276177960532</v>
+        <v>1.753273147931224</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-10.23269690379239</v>
+        <v>-10.12603528717457</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.9615218470156717</v>
+        <v>-0.9188572003685445</v>
       </c>
       <c r="F1876" t="n">
-        <v>-2.39284953692766</v>
+        <v>-2.28618792030984</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.696203616658437</v>
+        <v>1.760200586629129</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.22900597883598</v>
+        <v>-10.12234436221816</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.9600454770331077</v>
+        <v>-0.9173808303859805</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.39284953692766</v>
+        <v>-2.28618792030984</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.696203616658437</v>
+        <v>1.760200586629129</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.43326415416585</v>
+        <v>-10.32660253754803</v>
       </c>
       <c r="E1878" t="n">
-        <v>-1.036235550046411</v>
+        <v>-0.9935709033992834</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.520488481541649</v>
+        <v>-2.413826864923829</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.625133447008686</v>
+        <v>1.689130416979377</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.59390318065421</v>
+        <v>-10.48724156403639</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.096008606157321</v>
+        <v>-1.053343959510193</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.635221954544045</v>
+        <v>-2.528560337926225</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.560775917691684</v>
+        <v>1.624772887662376</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.52043334898676</v>
+        <v>-10.41377173236894</v>
       </c>
       <c r="E1880" t="n">
-        <v>-1.05124897199692</v>
+        <v>-1.008584325349792</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.561752122876596</v>
+        <v>-2.455090506258776</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.620229518185575</v>
+        <v>1.684226488156267</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.69555776637331</v>
+        <v>-10.58889614975549</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.106743518204021</v>
+        <v>-1.064078871556893</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.73687654026314</v>
+        <v>-2.63021492364532</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.529710088501165</v>
+        <v>1.593707058471857</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.93000986038779</v>
+        <v>-10.82334824376998</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.207743520711413</v>
+        <v>-1.165078874064285</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.73687654026314</v>
+        <v>-2.63021492364532</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.522490923599569</v>
+        <v>1.586487893570261</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-11.21781370492503</v>
+        <v>-11.11115208830721</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.329537249300284</v>
+        <v>-1.286872602653157</v>
       </c>
       <c r="F1883" t="n">
-        <v>-3.024680384800378</v>
+        <v>-2.918018768182558</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.34313642610325</v>
+        <v>1.407133396073942</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-11.44763815208886</v>
+        <v>-11.34097653547104</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.420351238327258</v>
+        <v>-1.37768659168013</v>
       </c>
       <c r="F1884" t="n">
-        <v>-3.187327921870539</v>
+        <v>-3.080666305252719</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.24666369369971</v>
+        <v>1.310660663670402</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-11.67966707182512</v>
+        <v>-11.5730054552073</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.510469077592648</v>
+        <v>-1.467804430945521</v>
       </c>
       <c r="F1885" t="n">
-        <v>-3.249340619058962</v>
+        <v>-3.142679002441142</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.212149804015771</v>
+        <v>1.276146773986463</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-11.62765155785631</v>
+        <v>-11.52098994123849</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.485672536318722</v>
+        <v>-1.443007889671594</v>
       </c>
       <c r="F1886" t="n">
-        <v>-3.249340619058962</v>
+        <v>-3.142679002441142</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.216140139702172</v>
+        <v>1.280137109672864</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-11.76932339958043</v>
+        <v>-11.66266178296261</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.543816499907112</v>
+        <v>-1.501151853259984</v>
       </c>
       <c r="F1887" t="n">
-        <v>-3.249340619058962</v>
+        <v>-3.142679002441142</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.21466491280343</v>
+        <v>1.278661882774122</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-11.8682301400397</v>
+        <v>-11.76156852342188</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.568325785925949</v>
+        <v>-1.525661139278822</v>
       </c>
       <c r="F1888" t="n">
-        <v>-3.348247359518238</v>
+        <v>-3.241585742900418</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.170374278692737</v>
+        <v>1.234371248663429</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-11.6690780328026</v>
+        <v>-11.56241641618479</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.501716076677793</v>
+        <v>-1.459051430030665</v>
       </c>
       <c r="F1889" t="n">
-        <v>-3.182924833568424</v>
+        <v>-3.076263216950605</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.256516660615942</v>
+        <v>1.320513630586634</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-11.44323288008319</v>
+        <v>-11.33657126346537</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.401798942553821</v>
+        <v>-1.359134295906692</v>
       </c>
       <c r="F1890" t="n">
-        <v>-3.140998157981261</v>
+        <v>-3.034336541363441</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.291251739004449</v>
+        <v>1.35524870897514</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.1569580677605</v>
+        <v>-11.05029645114268</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.286149873068684</v>
+        <v>-1.243485226421555</v>
       </c>
       <c r="F1891" t="n">
-        <v>-3.140998157981261</v>
+        <v>-3.034336541363441</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.292390883560508</v>
+        <v>1.356387853531199</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.20985335580479</v>
+        <v>-11.10319173918696</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.30467421412429</v>
+        <v>-1.262009567477162</v>
       </c>
       <c r="F1892" t="n">
-        <v>-3.136042811892815</v>
+        <v>-3.029381195274995</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.297997865375683</v>
+        <v>1.361994835346375</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.92594462487604</v>
+        <v>-10.81928300825822</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.185377017514154</v>
+        <v>-1.142712370867026</v>
       </c>
       <c r="F1893" t="n">
-        <v>-3.136042811892815</v>
+        <v>-3.029381195274995</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.303731569614319</v>
+        <v>1.367728539585011</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.67895737468309</v>
+        <v>-10.57229575806526</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.096319379830839</v>
+        <v>-1.053654733183711</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.889055561699863</v>
+        <v>-2.782393945082043</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.442186657336225</v>
+        <v>1.506183627306917</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.41512050747902</v>
+        <v>-10.30845889086119</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.000668114262119</v>
+        <v>-0.9580034676149904</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.889055561699863</v>
+        <v>-2.782393945082043</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.432303176023318</v>
+        <v>1.49630014599401</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.14787870661062</v>
+        <v>-10.0412170899928</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.8956059544141328</v>
+        <v>-0.8529413077670047</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.889055561699863</v>
+        <v>-2.782393945082043</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.430468615523944</v>
+        <v>1.494465585494636</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.872069543210133</v>
+        <v>-9.765407926592312</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.7855826040273999</v>
+        <v>-0.7429179573802718</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.800036253421129</v>
+        <v>-2.693374636803309</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.483579885517723</v>
+        <v>1.547576855488415</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.848116002234175</v>
+        <v>-9.741454385616354</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.7753326814915233</v>
+        <v>-0.7326680348443948</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.776082712445171</v>
+        <v>-2.669421095827352</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.498620516248791</v>
+        <v>1.562617486219483</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.584056063911378</v>
+        <v>-9.477394447293557</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.6829690223241567</v>
+        <v>-0.6403043756770286</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.512022774122376</v>
+        <v>-2.405361157504556</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.643796163080717</v>
+        <v>1.707793133051409</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.876976440406541</v>
+        <v>-8.77031482378872</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.4029242065825227</v>
+        <v>-0.3602595599353942</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.512022774122376</v>
+        <v>-2.405361157504556</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.641009129420416</v>
+        <v>1.705006099391108</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.83679214204035</v>
+        <v>-8.730130525422529</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.3865068633482052</v>
+        <v>-0.3438422167010766</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.471838475756185</v>
+        <v>-2.365176859138365</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.665463332327972</v>
+        <v>1.729460302298664</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096478</v>
+        <v>3.856158176096477</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.582250242699274</v>
+        <v>-8.475588626081453</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.2853232823910177</v>
+        <v>-0.2426586357438896</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.217296576415109</v>
+        <v>-2.110634959797289</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.817555293153374</v>
+        <v>1.881552263124066</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.78732685376181</v>
+        <v>3.787326853761808</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.348769020469675</v>
+        <v>-8.242107403851854</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.1840063646613257</v>
+        <v>-0.1413417180141971</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.983815354185511</v>
+        <v>-1.877153737567691</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.965568455328985</v>
+        <v>2.029565425299678</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255786</v>
+        <v>3.801633547255785</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.169060490325801</v>
+        <v>-8.062398873707981</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.1150151629167353</v>
+        <v>-0.0723505162696072</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.926643850022814</v>
+        <v>-1.819982233404995</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.996979147513644</v>
+        <v>2.060976117484336</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860429</v>
+        <v>3.763178672860427</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.036785016694914</v>
+        <v>-7.930123400077094</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.06673748671735336</v>
+        <v>-0.0240728400702257</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.794368376391928</v>
+        <v>-1.687706759774108</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.071711918439203</v>
+        <v>2.135708888409895</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575955</v>
+        <v>3.784715218575953</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.846185342021761</v>
+        <v>-7.739523725403942</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.01231744383954414</v>
+        <v>0.05498209048667224</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.603768701718775</v>
+        <v>-1.497107085100955</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.188886783930732</v>
+        <v>2.252883753901423</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.75387899643099</v>
+        <v>3.753878996430988</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.59718554333818</v>
+        <v>-7.49052392672036</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.1248237045366354</v>
+        <v>0.1674883511837635</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.603768701718775</v>
+        <v>-1.497107085100955</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.20179312515439</v>
+        <v>2.265790095125082</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077647</v>
+        <v>3.692928280077645</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.702775533111285</v>
+        <v>-7.596113916493465</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.04538822097182482</v>
+        <v>-0.002723574324697164</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.709358691491879</v>
+        <v>-1.602697074874059</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.010463201691309</v>
+        <v>2.074460171662001</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457905</v>
+        <v>3.770419008457903</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.721510435229882</v>
+        <v>-7.614848818612062</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.004337839942177624</v>
+        <v>0.03832680670495048</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.709358691491879</v>
+        <v>-1.602697074874059</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.059007543568395</v>
+        <v>2.123004513539087</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180811</v>
+        <v>3.760330111180809</v>
       </c>
       <c r="C1910" t="n">
         <v>3.088001770449517</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.44477226055907</v>
+        <v>-7.338110643941249</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.1097364419121418</v>
+        <v>0.1524010885592704</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.527542030381953</v>
+        <v>-1.420880413764134</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.171476552220346</v>
+        <v>2.235473522191037</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879204</v>
+        <v>3.723562653879203</v>
       </c>
       <c r="C1911" t="n">
         <v>3.079287784196039</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.317879854124</v>
+        <v>-7.211218237506179</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.1517794182326919</v>
+        <v>0.19444406487982</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.400649623946884</v>
+        <v>-1.293988007329064</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.238898009827909</v>
+        <v>2.302894979798601</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568108</v>
+        <v>3.729966140568107</v>
       </c>
       <c r="C1912" t="n">
         <v>3.072327172100946</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.130292346214073</v>
+        <v>-7.023630729596253</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.2198538093015694</v>
+        <v>0.2625184559486975</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.400649623946884</v>
+        <v>-1.293988007329064</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.231937397732816</v>
+        <v>2.295934367703508</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.78291895796342</v>
+        <v>3.782918957963418</v>
       </c>
       <c r="C1913" t="n">
         <v>3.086789526482089</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.888143952760215</v>
+        <v>-6.781482336142394</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.3311755210642557</v>
+        <v>0.3738401677113838</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.400649623946884</v>
+        <v>-1.293988007329064</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.246399752113959</v>
+        <v>2.310396722084651</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192818</v>
+        <v>3.828547911192817</v>
       </c>
       <c r="C1914" t="n">
         <v>3.081321646941284</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.824914580991867</v>
+        <v>-6.718252964374046</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.3509993902307902</v>
+        <v>0.3936640368779183</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.400649623946884</v>
+        <v>-1.293988007329064</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.240931872573154</v>
+        <v>2.304928842543846</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262049</v>
+        <v>3.828049353262047</v>
       </c>
       <c r="C1915" t="n">
         <v>3.078819740951861</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.638426888614861</v>
+        <v>-6.53176527199704</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.4230925611921692</v>
+        <v>0.4657572078392977</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.214161931569877</v>
+        <v>-1.107500314952057</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.350322582009935</v>
+        <v>2.414319551980627</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389911</v>
+        <v>3.812450103389909</v>
       </c>
       <c r="C1916" t="n">
         <v>3.086520719189187</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.617277689711417</v>
+        <v>-6.510616073093597</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.4392532189908724</v>
+        <v>0.4819178656380005</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.193012732666434</v>
+        <v>-1.086351116048614</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.370713079589327</v>
+        <v>2.434710049560018</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788096</v>
+        <v>3.748324832788095</v>
       </c>
       <c r="C1917" t="n">
         <v>3.082301427536237</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.373512247727973</v>
+        <v>-6.266850631110152</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.5325401041313005</v>
+        <v>0.575204750778429</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.193012732666434</v>
+        <v>-1.086351116048614</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.366493787936377</v>
+        <v>2.430490757907069</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527528</v>
+        <v>3.824307657527526</v>
       </c>
       <c r="C1918" t="n">
         <v>3.084425741456253</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.109484180534713</v>
+        <v>-6.002822563916892</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.6402756449286207</v>
+        <v>0.6829402915757492</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.9911473338504804</v>
+        <v>-0.8844857172326606</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.489737341145966</v>
+        <v>2.553734311116657</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749186</v>
+        <v>3.826351398749185</v>
       </c>
       <c r="C1919" t="n">
         <v>3.077167816439955</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.859633786585638</v>
+        <v>-5.752972169967817</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.7329578774919527</v>
+        <v>0.7756225241390813</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.9911473338504804</v>
+        <v>-0.8844857172326606</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.482479416129667</v>
+        <v>2.546476386100359</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.8359544114815</v>
+        <v>3.835954411481498</v>
       </c>
       <c r="C1920" t="n">
         <v>3.080766939960604</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.556066297581659</v>
+        <v>-5.449404680963839</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.8579839966141933</v>
+        <v>0.9006486432613214</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.9911473338504804</v>
+        <v>-0.8844857172326606</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.486078539650316</v>
+        <v>2.550075509621008</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862989</v>
+        <v>3.780930335862987</v>
       </c>
       <c r="C1921" t="n">
         <v>3.094094446015158</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.482586388729645</v>
+        <v>-5.375924772111825</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.9007034662095523</v>
+        <v>0.9433681128566809</v>
       </c>
       <c r="F1921" t="n">
-        <v>-0.917667424998466</v>
+        <v>-0.8110058083806462</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.543493991016079</v>
+        <v>2.60749096098677</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102784</v>
+        <v>3.773761647102782</v>
       </c>
       <c r="C1922" t="n">
         <v>3.093114923631455</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.257553389060822</v>
+        <v>-5.150891772443002</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.9897371436933784</v>
+        <v>1.032401790340507</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.6926344253296431</v>
+        <v>-0.5859728087118233</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.677534268433669</v>
+        <v>2.741531238404361</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353079</v>
+        <v>3.764614304353077</v>
       </c>
       <c r="C1923" t="n">
         <v>3.097809724685772</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.042919011424416</v>
+        <v>-4.936257394806595</v>
       </c>
       <c r="E1923" t="n">
-        <v>1.080285695802258</v>
+        <v>1.122950342449387</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.4780000476932363</v>
+        <v>-0.3713384310754165</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.811009696069831</v>
+        <v>2.875006666040522</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544786</v>
+        <v>3.798811195544785</v>
       </c>
       <c r="C1924" t="n">
         <v>3.079003983469568</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.776318654450064</v>
+        <v>-4.669657037832243</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.168120097375795</v>
+        <v>1.210784744022923</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.4780000476932363</v>
+        <v>-0.3713384310754165</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.792203954853626</v>
+        <v>2.856200924824318</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712298</v>
+        <v>3.797691308712296</v>
       </c>
       <c r="C1925" t="n">
         <v>3.080747060094445</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.535888157645203</v>
+        <v>-4.429226541027383</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.266035372722616</v>
+        <v>1.308700019369745</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.2375695508883761</v>
+        <v>-0.1309079342705562</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.93820532956142</v>
+        <v>3.002202299532112</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837689</v>
+        <v>3.821589933837688</v>
       </c>
       <c r="C1926" t="n">
         <v>3.084676373929265</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.293097349995758</v>
+        <v>-4.186435733377937</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.367081009617215</v>
+        <v>1.409745656264343</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.2375695508883761</v>
+        <v>-0.1309079342705562</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.94213464339624</v>
+        <v>3.006131613366932</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822323422349971</v>
+        <v>3.822323422349969</v>
       </c>
       <c r="C1927" t="n">
         <v>3.085354957846605</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.053492258388669</v>
+        <v>-3.946830641770848</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.46360163017739</v>
+        <v>1.506266276824519</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.1705216032198815</v>
+        <v>-0.06385998660206171</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.983041995914677</v>
+        <v>3.047038965885369</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848613050972345</v>
+        <v>3.848613050972343</v>
       </c>
       <c r="C1928" t="n">
         <v>3.082353029066599</v>
       </c>
       <c r="D1928" t="n">
-        <v>-3.810836669965506</v>
+        <v>-3.704175053347685</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.557661936766649</v>
+        <v>1.600326583413778</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.1705216032198815</v>
+        <v>-0.06385998660206171</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.98004006713467</v>
+        <v>3.044037037105362</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145945</v>
+        <v>3.818665376145943</v>
       </c>
       <c r="C1929" t="n">
         <v>3.083932066077213</v>
       </c>
       <c r="D1929" t="n">
-        <v>-3.799358772256716</v>
+        <v>-3.692697155638895</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.563832132860779</v>
+        <v>1.606496779507907</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.1693253894028589</v>
+        <v>-0.0626637727850391</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.982336832435498</v>
+        <v>3.04633380240619</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.540533056027617</v>
+        <v>3.851952635846496</v>
       </c>
       <c r="C1930" t="n">
-        <v>2.866109101754391</v>
+        <v>3.180525595192078</v>
       </c>
       <c r="D1930" t="n">
-        <v>-3.799358772256716</v>
+        <v>-3.692697155638895</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.563832132860779</v>
+        <v>1.606496779507907</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.1693253894028589</v>
+        <v>-0.0626637727850391</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.859172898740759</v>
+        <v>3.173589392178445</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240410.xlsx
+++ b/tame_output/ON/bt/strategyON_20240410.xlsx
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-77.7%</t>
+          <t>-77.0%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>117.2%</t>
+          <t>117.6%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>136.1%</t>
+          <t>136.2%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>97.0%</t>
+          <t>97.9%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-683.5%</t>
+          <t>-684.8%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>28.0%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-73.4%</t>
+          <t>-72.4%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>97.2%</t>
+          <t>97.6%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>5.5%</t>
+          <t>5.1%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-530.8%</t>
+          <t>-511.3%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>15.8%</t>
+          <t>17.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>46.1%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-268.0%</t>
+          <t>-268.5%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>14.1%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>14.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>45.9%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-79.7%</t>
+          <t>-86.2%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>37.1%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-215.6%</t>
+          <t>-207.7%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-25.8%</t>
+          <t>-24.2%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>69.7%</t>
+          <t>70.0%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>69.6%</t>
+          <t>69.7%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>69.8%</t>
+          <t>70.6%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.7%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-18.4%</t>
+          <t>-16.5%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>57.8%</t>
+          <t>58.1%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>32.8%</t>
+          <t>32.6%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-154.7%</t>
+          <t>-168.7%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-230.3%</t>
+          <t>-217.5%</t>
         </is>
       </c>
     </row>
@@ -1390,12 +1390,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>58.6%</t>
+          <t>58.7%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>51.0%</t>
+          <t>50.9%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>61.8%</t>
+          <t>61.9%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>42.1%</t>
+          <t>41.9%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>97.2%</t>
+          <t>97.3%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-30.5%</t>
+          <t>-30.6%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>52.7%</t>
+          <t>52.9%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297756</v>
+        <v>3.458100091297755</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.446581082799119</v>
+        <v>-9.459405155904145</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.6633835924953591</v>
+        <v>-0.6685132217373693</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.966264038438387</v>
+        <v>-1.979088111543413</v>
       </c>
       <c r="G1873" t="n">
-        <v>1.935846841875004</v>
+        <v>1.928152398011989</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.80611140530312</v>
+        <v>-9.818935478408147</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.8018454181989094</v>
+        <v>-0.8069750474409201</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.966264038438387</v>
+        <v>-1.979088111543413</v>
       </c>
       <c r="G1874" t="n">
-        <v>1.941197145173054</v>
+        <v>1.933502701310038</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-10.13251143396813</v>
+        <v>-10.14533550707316</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.924489409707737</v>
+        <v>-0.9296190389497476</v>
       </c>
       <c r="F1875" t="n">
-        <v>-2.2926640671034</v>
+        <v>-2.305488140208426</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.753273147931224</v>
+        <v>1.745578704068208</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-10.12603528717457</v>
+        <v>-10.1388593602796</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.9188572003685445</v>
+        <v>-0.9239868296105551</v>
       </c>
       <c r="F1876" t="n">
-        <v>-2.28618792030984</v>
+        <v>-2.299011993414867</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.760200586629129</v>
+        <v>1.752506142766113</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.12234436221816</v>
+        <v>-10.13516843532319</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.9173808303859805</v>
+        <v>-0.9225104596279903</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.28618792030984</v>
+        <v>-2.299011993414867</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.760200586629129</v>
+        <v>1.752506142766113</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.32660253754803</v>
+        <v>-10.33942661065305</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.9935709033992834</v>
+        <v>-0.9987005326412941</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.413826864923829</v>
+        <v>-2.426650938028855</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.689130416979377</v>
+        <v>1.681435973116362</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.48724156403639</v>
+        <v>-10.50006563714142</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.053343959510193</v>
+        <v>-1.058473588752204</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.528560337926225</v>
+        <v>-2.541384411031251</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.624772887662376</v>
+        <v>1.61707844379936</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.41377173236894</v>
+        <v>-10.42659580547397</v>
       </c>
       <c r="E1880" t="n">
-        <v>-1.008584325349792</v>
+        <v>-1.013713954591803</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.455090506258776</v>
+        <v>-2.467914579363803</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.684226488156267</v>
+        <v>1.676532044293251</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.58889614975549</v>
+        <v>-10.60172022286051</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.064078871556893</v>
+        <v>-1.069208500798903</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.63021492364532</v>
+        <v>-2.643038996750346</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.593707058471857</v>
+        <v>1.586012614608841</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.82334824376998</v>
+        <v>-10.836172316875</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.165078874064285</v>
+        <v>-1.170208503306295</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.63021492364532</v>
+        <v>-2.643038996750346</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.586487893570261</v>
+        <v>1.578793449707245</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-11.11115208830721</v>
+        <v>-11.12397616141224</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.286872602653157</v>
+        <v>-1.292002231895167</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.918018768182558</v>
+        <v>-2.930842841287585</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.407133396073942</v>
+        <v>1.399438952210926</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-11.34097653547104</v>
+        <v>-11.35380060857607</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.37768659168013</v>
+        <v>-1.382816220922141</v>
       </c>
       <c r="F1884" t="n">
-        <v>-3.080666305252719</v>
+        <v>-3.093490378357745</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.310660663670402</v>
+        <v>1.302966219807386</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-11.5730054552073</v>
+        <v>-11.58582952831233</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.467804430945521</v>
+        <v>-1.47293406018753</v>
       </c>
       <c r="F1885" t="n">
-        <v>-3.142679002441142</v>
+        <v>-3.155503075546168</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.276146773986463</v>
+        <v>1.268452330123447</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-11.52098994123849</v>
+        <v>-11.53381401434351</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.443007889671594</v>
+        <v>-1.448137518913605</v>
       </c>
       <c r="F1886" t="n">
-        <v>-3.142679002441142</v>
+        <v>-3.155503075546168</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.280137109672864</v>
+        <v>1.272442665809848</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-11.66266178296261</v>
+        <v>-11.67548585606763</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.501151853259984</v>
+        <v>-1.506281482501994</v>
       </c>
       <c r="F1887" t="n">
-        <v>-3.142679002441142</v>
+        <v>-3.155503075546168</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.278661882774122</v>
+        <v>1.270967438911106</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-11.76156852342188</v>
+        <v>-11.77439259652691</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.525661139278822</v>
+        <v>-1.530790768520833</v>
       </c>
       <c r="F1888" t="n">
-        <v>-3.241585742900418</v>
+        <v>-3.254409816005444</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.234371248663429</v>
+        <v>1.226676804800413</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-11.56241641618479</v>
+        <v>-11.57524048928981</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.459051430030665</v>
+        <v>-1.464181059272676</v>
       </c>
       <c r="F1889" t="n">
-        <v>-3.076263216950605</v>
+        <v>-3.089087290055631</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.320513630586634</v>
+        <v>1.312819186723618</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-11.33657126346537</v>
+        <v>-11.3493953365704</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.359134295906692</v>
+        <v>-1.364263925148702</v>
       </c>
       <c r="F1890" t="n">
-        <v>-3.034336541363441</v>
+        <v>-3.047160614468467</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.35524870897514</v>
+        <v>1.347554265112125</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.05029645114268</v>
+        <v>-11.0631205242477</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.243485226421555</v>
+        <v>-1.248614855663565</v>
       </c>
       <c r="F1891" t="n">
-        <v>-3.034336541363441</v>
+        <v>-3.047160614468467</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.356387853531199</v>
+        <v>1.348693409668184</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.10319173918696</v>
+        <v>-11.11601581229199</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.262009567477162</v>
+        <v>-1.267139196719173</v>
       </c>
       <c r="F1892" t="n">
-        <v>-3.029381195274995</v>
+        <v>-3.042205268380021</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.361994835346375</v>
+        <v>1.354300391483359</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.81928300825822</v>
+        <v>-10.83210708136324</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.142712370867026</v>
+        <v>-1.147842000109036</v>
       </c>
       <c r="F1893" t="n">
-        <v>-3.029381195274995</v>
+        <v>-3.042205268380021</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.367728539585011</v>
+        <v>1.360034095721995</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.57229575806526</v>
+        <v>-10.58511983117029</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.053654733183711</v>
+        <v>-1.058784362425721</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.782393945082043</v>
+        <v>-2.795218018187069</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.506183627306917</v>
+        <v>1.498489183443901</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.30845889086119</v>
+        <v>-10.32128296396622</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.9580034676149904</v>
+        <v>-0.9631330968570011</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.782393945082043</v>
+        <v>-2.795218018187069</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.49630014599401</v>
+        <v>1.488605702130994</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.0412170899928</v>
+        <v>-10.05404116309782</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.8529413077670047</v>
+        <v>-0.8580709370090154</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.782393945082043</v>
+        <v>-2.795218018187069</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.494465585494636</v>
+        <v>1.48677114163162</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.765407926592312</v>
+        <v>-9.778231999697338</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.7429179573802718</v>
+        <v>-0.7480475866222824</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.693374636803309</v>
+        <v>-2.706198709908335</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.547576855488415</v>
+        <v>1.5398824116254</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.741454385616354</v>
+        <v>-9.75427845872138</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.7326680348443948</v>
+        <v>-0.7377976640864055</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.669421095827352</v>
+        <v>-2.682245168932378</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.562617486219483</v>
+        <v>1.554923042356467</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.477394447293557</v>
+        <v>-9.490218520398583</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.6403043756770286</v>
+        <v>-0.6454340049190388</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.405361157504556</v>
+        <v>-2.418185230609582</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.707793133051409</v>
+        <v>1.700098689188393</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.77031482378872</v>
+        <v>-8.783138896893746</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.3602595599353942</v>
+        <v>-0.3653891891774048</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.405361157504556</v>
+        <v>-2.418185230609582</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.705006099391108</v>
+        <v>1.697311655528092</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.730130525422529</v>
+        <v>-8.742954598527556</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.3438422167010766</v>
+        <v>-0.3489718459430873</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.365176859138365</v>
+        <v>-2.378000932243391</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.729460302298664</v>
+        <v>1.721765858435648</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096477</v>
+        <v>3.856158176096478</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.475588626081453</v>
+        <v>-8.48841269918648</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.2426586357438896</v>
+        <v>-0.2477882649858998</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.110634959797289</v>
+        <v>-2.123459032902316</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.881552263124066</v>
+        <v>1.87385781926105</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761808</v>
+        <v>3.78732685376181</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.242107403851854</v>
+        <v>-8.25493147695688</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.1413417180141971</v>
+        <v>-0.1464713472562078</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.877153737567691</v>
+        <v>-1.889977810672717</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.029565425299678</v>
+        <v>2.021870981436662</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255785</v>
+        <v>3.801633547255786</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.062398873707981</v>
+        <v>-8.075222946813007</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.0723505162696072</v>
+        <v>-0.07748014551161742</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.819982233404995</v>
+        <v>-1.832806306510021</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.060976117484336</v>
+        <v>2.05328167362132</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860427</v>
+        <v>3.763178672860429</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-7.930123400077094</v>
+        <v>-7.94294747318212</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.0240728400702257</v>
+        <v>-0.02920246931223591</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.687706759774108</v>
+        <v>-1.700530832879134</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.135708888409895</v>
+        <v>2.12801444454688</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575953</v>
+        <v>3.784715218575955</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.739523725403942</v>
+        <v>-7.752347798508968</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.05498209048667224</v>
+        <v>0.04985246124466158</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.497107085100955</v>
+        <v>-1.509931158205981</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.252883753901423</v>
+        <v>2.245189310038408</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430988</v>
+        <v>3.75387899643099</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.49052392672036</v>
+        <v>-7.503347999825387</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.1674883511837635</v>
+        <v>0.1623587219417528</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.497107085100955</v>
+        <v>-1.509931158205981</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.265790095125082</v>
+        <v>2.258095651262066</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077645</v>
+        <v>3.692928280077647</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.596113916493465</v>
+        <v>-7.608937989598491</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.002723574324697164</v>
+        <v>-0.007853203566707379</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.602697074874059</v>
+        <v>-1.615521147979086</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.074460171662001</v>
+        <v>2.066765727798985</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457903</v>
+        <v>3.770419008457905</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.614848818612062</v>
+        <v>-7.627672891717088</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.03832680670495048</v>
+        <v>0.03319717746293982</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.602697074874059</v>
+        <v>-1.615521147979086</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.123004513539087</v>
+        <v>2.115310069676072</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180809</v>
+        <v>3.760330111180811</v>
       </c>
       <c r="C1910" t="n">
         <v>3.088001770449517</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.338110643941249</v>
+        <v>-7.350934717046275</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.1524010885592704</v>
+        <v>0.1472714593172597</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.420880413764134</v>
+        <v>-1.43370448686916</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.235473522191037</v>
+        <v>2.227779078328022</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879203</v>
+        <v>3.723562653879204</v>
       </c>
       <c r="C1911" t="n">
         <v>3.079287784196039</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.211218237506179</v>
+        <v>-7.224042310611205</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.19444406487982</v>
+        <v>0.1893144356378098</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.293988007329064</v>
+        <v>-1.30681208043409</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.302894979798601</v>
+        <v>2.295200535935586</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568107</v>
+        <v>3.729966140568108</v>
       </c>
       <c r="C1912" t="n">
         <v>3.072327172100946</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.023630729596253</v>
+        <v>-7.036454802701279</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.2625184559486975</v>
+        <v>0.2573888267066873</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.293988007329064</v>
+        <v>-1.30681208043409</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.295934367703508</v>
+        <v>2.288239923840492</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963418</v>
+        <v>3.78291895796342</v>
       </c>
       <c r="C1913" t="n">
         <v>3.086789526482089</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.781482336142394</v>
+        <v>-6.794306409247421</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.3738401677113838</v>
+        <v>0.3687105384693736</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.293988007329064</v>
+        <v>-1.30681208043409</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.310396722084651</v>
+        <v>2.302702278221636</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192817</v>
+        <v>3.828547911192818</v>
       </c>
       <c r="C1914" t="n">
         <v>3.081321646941284</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.718252964374046</v>
+        <v>-6.731077037479072</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.3936640368779183</v>
+        <v>0.3885344076359076</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.293988007329064</v>
+        <v>-1.30681208043409</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.304928842543846</v>
+        <v>2.297234398680831</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262047</v>
+        <v>3.828049353262049</v>
       </c>
       <c r="C1915" t="n">
         <v>3.078819740951861</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.53176527199704</v>
+        <v>-6.544589345102066</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.4657572078392977</v>
+        <v>0.4606275785972871</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.107500314952057</v>
+        <v>-1.120324388057084</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.414319551980627</v>
+        <v>2.406625108117611</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389909</v>
+        <v>3.812450103389911</v>
       </c>
       <c r="C1916" t="n">
         <v>3.086520719189187</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.510616073093597</v>
+        <v>-6.523440146198623</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.4819178656380005</v>
+        <v>0.4767882363959899</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.086351116048614</v>
+        <v>-1.09917518915364</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.434710049560018</v>
+        <v>2.427015605697003</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788095</v>
+        <v>3.748324832788096</v>
       </c>
       <c r="C1917" t="n">
         <v>3.082301427536237</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.266850631110152</v>
+        <v>-6.279674704215179</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.575204750778429</v>
+        <v>0.5700751215364184</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.086351116048614</v>
+        <v>-1.09917518915364</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.430490757907069</v>
+        <v>2.422796314044053</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527526</v>
+        <v>3.824307657527528</v>
       </c>
       <c r="C1918" t="n">
         <v>3.084425741456253</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.002822563916892</v>
+        <v>-6.015646637021918</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.6829402915757492</v>
+        <v>0.6778106623337385</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.8844857172326606</v>
+        <v>-0.8973097903376868</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.553734311116657</v>
+        <v>2.546039867253642</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749185</v>
+        <v>3.826351398749186</v>
       </c>
       <c r="C1919" t="n">
         <v>3.077167816439955</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.752972169967817</v>
+        <v>-5.765796243072844</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.7756225241390813</v>
+        <v>0.7704928948970706</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.8844857172326606</v>
+        <v>-0.8973097903376868</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.546476386100359</v>
+        <v>2.538781942237343</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481498</v>
+        <v>3.8359544114815</v>
       </c>
       <c r="C1920" t="n">
         <v>3.080766939960604</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.449404680963839</v>
+        <v>-5.462228754068865</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.9006486432613214</v>
+        <v>0.8955190140193108</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.8844857172326606</v>
+        <v>-0.8973097903376868</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.550075509621008</v>
+        <v>2.542381065757993</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862987</v>
+        <v>3.780930335862989</v>
       </c>
       <c r="C1921" t="n">
         <v>3.094094446015158</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.375924772111825</v>
+        <v>-5.388748845216851</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.9433681128566809</v>
+        <v>0.9382384836146702</v>
       </c>
       <c r="F1921" t="n">
-        <v>-0.8110058083806462</v>
+        <v>-0.8238298814856724</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.60749096098677</v>
+        <v>2.599796517123755</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102782</v>
+        <v>3.773761647102784</v>
       </c>
       <c r="C1922" t="n">
         <v>3.093114923631455</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.150891772443002</v>
+        <v>-5.163715845548028</v>
       </c>
       <c r="E1922" t="n">
-        <v>1.032401790340507</v>
+        <v>1.027272161098496</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.5859728087118233</v>
+        <v>-0.5987968818168495</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.741531238404361</v>
+        <v>2.733836794541345</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353077</v>
+        <v>3.764614304353079</v>
       </c>
       <c r="C1923" t="n">
         <v>3.097809724685772</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.936257394806595</v>
+        <v>-4.949081467911621</v>
       </c>
       <c r="E1923" t="n">
-        <v>1.122950342449387</v>
+        <v>1.117820713207376</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.3713384310754165</v>
+        <v>-0.3841625041804427</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.875006666040522</v>
+        <v>2.867312222177507</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544785</v>
+        <v>3.798811195544786</v>
       </c>
       <c r="C1924" t="n">
         <v>3.079003983469568</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.669657037832243</v>
+        <v>-4.682481110937269</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.210784744022923</v>
+        <v>1.205655114780913</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.3713384310754165</v>
+        <v>-0.3841625041804427</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.856200924824318</v>
+        <v>2.848506480961302</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712296</v>
+        <v>3.797691308712298</v>
       </c>
       <c r="C1925" t="n">
         <v>3.080747060094445</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.429226541027383</v>
+        <v>-4.442050614132409</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.308700019369745</v>
+        <v>1.303570390127734</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.1309079342705562</v>
+        <v>-0.1437320073755824</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.002202299532112</v>
+        <v>2.994507855669096</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837688</v>
+        <v>3.821589933837689</v>
       </c>
       <c r="C1926" t="n">
         <v>3.084676373929265</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.186435733377937</v>
+        <v>-4.199259806482964</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.409745656264343</v>
+        <v>1.404616027022333</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.1309079342705562</v>
+        <v>-0.1437320073755824</v>
       </c>
       <c r="G1926" t="n">
-        <v>3.006131613366932</v>
+        <v>2.998437169503916</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822323422349969</v>
+        <v>3.822323422349971</v>
       </c>
       <c r="C1927" t="n">
         <v>3.085354957846605</v>
       </c>
       <c r="D1927" t="n">
-        <v>-3.946830641770848</v>
+        <v>-3.959654714875874</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.506266276824519</v>
+        <v>1.501136647582508</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.06385998660206171</v>
+        <v>-0.07668405970708791</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.047038965885369</v>
+        <v>3.039344522022353</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848613050972343</v>
+        <v>3.848613050972345</v>
       </c>
       <c r="C1928" t="n">
         <v>3.082353029066599</v>
       </c>
       <c r="D1928" t="n">
-        <v>-3.704175053347685</v>
+        <v>-3.716999126452711</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.600326583413778</v>
+        <v>1.595196954171767</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.06385998660206171</v>
+        <v>-0.07668405970708791</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.044037037105362</v>
+        <v>3.036342593242346</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145943</v>
+        <v>3.818665376145945</v>
       </c>
       <c r="C1929" t="n">
         <v>3.083932066077213</v>
       </c>
       <c r="D1929" t="n">
-        <v>-3.692697155638895</v>
+        <v>-3.4969783284157</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.606496779507907</v>
+        <v>1.684784310397186</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.0626637727850391</v>
+        <v>0.06453578536089233</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.04633380240619</v>
+        <v>3.122653537293749</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,19 +45935,19 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.851952635846496</v>
+        <v>3.851952635846498</v>
       </c>
       <c r="C1930" t="n">
         <v>3.180525595192078</v>
       </c>
       <c r="D1930" t="n">
-        <v>-3.692697155638895</v>
+        <v>-3.4969783284157</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.606496779507907</v>
+        <v>1.684784310397186</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.0626637727850391</v>
+        <v>0.06453578536089233</v>
       </c>
       <c r="G1930" t="n">
         <v>3.173589392178445</v>

--- a/tame_output/ON/bt/strategyON_20240410.xlsx
+++ b/tame_output/ON/bt/strategyON_20240410.xlsx
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.78732685376181</v>
+        <v>3.787326853761809</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
@@ -45337,7 +45337,7 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255786</v>
+        <v>3.801633547255785</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
@@ -45360,7 +45360,7 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860429</v>
+        <v>3.763178672860427</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
@@ -45383,7 +45383,7 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575955</v>
+        <v>3.784715218575953</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.75387899643099</v>
+        <v>3.753878996430988</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077647</v>
+        <v>3.692928280077645</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
@@ -45452,7 +45452,7 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457905</v>
+        <v>3.770419008457903</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180811</v>
+        <v>3.760330111180809</v>
       </c>
       <c r="C1910" t="n">
         <v>3.088001770449517</v>
@@ -45498,7 +45498,7 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879204</v>
+        <v>3.723562653879203</v>
       </c>
       <c r="C1911" t="n">
         <v>3.079287784196039</v>
@@ -45521,7 +45521,7 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568108</v>
+        <v>3.729966140568107</v>
       </c>
       <c r="C1912" t="n">
         <v>3.072327172100946</v>
@@ -45544,7 +45544,7 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.78291895796342</v>
+        <v>3.782918957963418</v>
       </c>
       <c r="C1913" t="n">
         <v>3.086789526482089</v>
@@ -45567,7 +45567,7 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192818</v>
+        <v>3.828547911192817</v>
       </c>
       <c r="C1914" t="n">
         <v>3.081321646941284</v>
@@ -45590,7 +45590,7 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262049</v>
+        <v>3.828049353262047</v>
       </c>
       <c r="C1915" t="n">
         <v>3.078819740951861</v>
@@ -45613,7 +45613,7 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389911</v>
+        <v>3.812450103389909</v>
       </c>
       <c r="C1916" t="n">
         <v>3.086520719189187</v>
@@ -45636,7 +45636,7 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788096</v>
+        <v>3.748324832788095</v>
       </c>
       <c r="C1917" t="n">
         <v>3.082301427536237</v>
@@ -45659,7 +45659,7 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527528</v>
+        <v>3.824307657527526</v>
       </c>
       <c r="C1918" t="n">
         <v>3.084425741456253</v>
@@ -45682,7 +45682,7 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749186</v>
+        <v>3.826351398749185</v>
       </c>
       <c r="C1919" t="n">
         <v>3.077167816439955</v>
@@ -45705,7 +45705,7 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.8359544114815</v>
+        <v>3.835954411481498</v>
       </c>
       <c r="C1920" t="n">
         <v>3.080766939960604</v>
@@ -45728,7 +45728,7 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862989</v>
+        <v>3.780930335862987</v>
       </c>
       <c r="C1921" t="n">
         <v>3.094094446015158</v>
@@ -45751,7 +45751,7 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102784</v>
+        <v>3.773761647102782</v>
       </c>
       <c r="C1922" t="n">
         <v>3.093114923631455</v>
@@ -45774,7 +45774,7 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353079</v>
+        <v>3.764614304353077</v>
       </c>
       <c r="C1923" t="n">
         <v>3.097809724685772</v>
@@ -45797,7 +45797,7 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544786</v>
+        <v>3.798811195544785</v>
       </c>
       <c r="C1924" t="n">
         <v>3.079003983469568</v>
@@ -45820,7 +45820,7 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712298</v>
+        <v>3.797691308712296</v>
       </c>
       <c r="C1925" t="n">
         <v>3.080747060094445</v>
@@ -45843,7 +45843,7 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837689</v>
+        <v>3.821589933837688</v>
       </c>
       <c r="C1926" t="n">
         <v>3.084676373929265</v>
@@ -45866,7 +45866,7 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822323422349971</v>
+        <v>3.822323422349969</v>
       </c>
       <c r="C1927" t="n">
         <v>3.085354957846605</v>
@@ -45889,7 +45889,7 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848613050972345</v>
+        <v>3.848613050972343</v>
       </c>
       <c r="C1928" t="n">
         <v>3.082353029066599</v>
@@ -45912,7 +45912,7 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145945</v>
+        <v>3.818665376145943</v>
       </c>
       <c r="C1929" t="n">
         <v>3.083932066077213</v>
@@ -45935,7 +45935,7 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.851952635846498</v>
+        <v>3.851952635846496</v>
       </c>
       <c r="C1930" t="n">
         <v>3.180525595192078</v>

--- a/tame_output/ON/bt/strategyON_20240410.xlsx
+++ b/tame_output/ON/bt/strategyON_20240410.xlsx
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>74.9%</t>
+          <t>72.4%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>29.1%</t>
+          <t>28.8%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>28.1%</t>
+          <t>27.6%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>6.8%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>59.8%</t>
+          <t>57.6%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>23.3%</t>
+          <t>23.0%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.4%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>6.4%</t>
+          <t>-1.6%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-77.0%</t>
+          <t>-77.3%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>117.6%</t>
+          <t>117.7%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>28.4%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-72.4%</t>
+          <t>-72.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>5.1%</t>
+          <t>5.2%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-511.3%</t>
+          <t>-517.2%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>17.5%</t>
+          <t>17.3%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>14.4%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>37.1%</t>
+          <t>37.0%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-207.7%</t>
+          <t>-208.5%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>58.7%</t>
+          <t>57.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>41.9%</t>
+          <t>41.8%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>52.9%</t>
+          <t>52.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>34.3%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-128.7%</t>
+          <t>-132.2%</t>
         </is>
       </c>
     </row>
@@ -45938,19 +45938,19 @@
         <v>3.851952635846496</v>
       </c>
       <c r="C1930" t="n">
-        <v>3.180525595192078</v>
+        <v>3.099826248879036</v>
       </c>
       <c r="D1930" t="n">
-        <v>-3.4969783284157</v>
+        <v>-3.556303768047496</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.684784310397186</v>
+        <v>1.67694831734629</v>
       </c>
       <c r="F1930" t="n">
         <v>0.06453578536089233</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.173589392178445</v>
+        <v>3.138547720095572</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240410.xlsx
+++ b/tame_output/ON/bt/strategyON_20240410.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>66.0%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.5%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-17.5%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.3%</t>
+          <t>18.7%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.9%</t>
+          <t>-12.4%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>28.7%</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>57.6%</t>
+          <t>59.2%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>23.0%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>39.1%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-77.3%</t>
+          <t>-77.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>117.7%</t>
+          <t>118.0%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>136.2%</t>
+          <t>137.2%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>97.9%</t>
+          <t>97.5%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-684.8%</t>
+          <t>-694.2%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>28.4%</t>
+          <t>28.7%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-55.2%</t>
+          <t>-55.6%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-72.7%</t>
+          <t>-73.0%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>97.6%</t>
+          <t>97.7%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>502.0%</t>
+          <t>499.7%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>5.2%</t>
+          <t>6.2%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-517.2%</t>
+          <t>-517.9%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>17.3%</t>
+          <t>17.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>55.1%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>65.2%</t>
+          <t>65.6%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-268.5%</t>
+          <t>-272.3%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>14.4%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-43.1%</t>
+          <t>-43.4%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>15.2%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>45.9%</t>
+          <t>46.1%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-86.2%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>37.0%</t>
+          <t>41.5%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-208.5%</t>
+          <t>-208.8%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-24.2%</t>
+          <t>-28.3%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>70.0%</t>
+          <t>70.1%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>69.7%</t>
+          <t>70.9%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>70.6%</t>
+          <t>68.2%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-35.4%</t>
+          <t>-36.0%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-16.5%</t>
+          <t>-21.7%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>58.1%</t>
+          <t>58.2%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>32.6%</t>
+          <t>33.5%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-168.7%</t>
+          <t>-153.7%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-217.5%</t>
+          <t>-244.4%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>57.6%</t>
+          <t>52.8%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>61.9%</t>
+          <t>62.7%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>41.8%</t>
+          <t>41.0%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>97.3%</t>
+          <t>97.4%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1466,22 +1466,22 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>12.1%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-30.6%</t>
+          <t>-31.1%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>52.0%</t>
+          <t>48.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.6%</t>
+          <t>-16.4%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.3%</t>
+          <t>34.0%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-132.2%</t>
+          <t>-148.3%</t>
         </is>
       </c>
     </row>
@@ -44624,22 +44624,22 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317622</v>
+        <v>3.447750501317621</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.459405155904145</v>
+        <v>-9.553242699416938</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.6685132217373693</v>
+        <v>-0.7060482391424867</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.979088111543413</v>
+        <v>-2.072925655056207</v>
       </c>
       <c r="G1873" t="n">
-        <v>1.928152398011989</v>
+        <v>1.871849871904312</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.818935478408147</v>
+        <v>-9.912773021920939</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.8069750474409201</v>
+        <v>-0.8445100648460371</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.979088111543413</v>
+        <v>-2.072925655056207</v>
       </c>
       <c r="G1874" t="n">
-        <v>1.933502701310038</v>
+        <v>1.877200175202362</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-10.14533550707316</v>
+        <v>-10.23917305058595</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.9296190389497476</v>
+        <v>-0.9671540563548651</v>
       </c>
       <c r="F1875" t="n">
-        <v>-2.305488140208426</v>
+        <v>-2.39932568372122</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.745578704068208</v>
+        <v>1.689276177960532</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-10.1388593602796</v>
+        <v>-10.23269690379239</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.9239868296105551</v>
+        <v>-0.9615218470156717</v>
       </c>
       <c r="F1876" t="n">
-        <v>-2.299011993414867</v>
+        <v>-2.39284953692766</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.752506142766113</v>
+        <v>1.696203616658437</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.13516843532319</v>
+        <v>-10.22900597883598</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.9225104596279903</v>
+        <v>-0.9600454770331077</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.299011993414867</v>
+        <v>-2.39284953692766</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.752506142766113</v>
+        <v>1.696203616658437</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.33942661065305</v>
+        <v>-10.43326415416585</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.9987005326412941</v>
+        <v>-1.036235550046411</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.426650938028855</v>
+        <v>-2.520488481541649</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.681435973116362</v>
+        <v>1.625133447008686</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.50006563714142</v>
+        <v>-10.59390318065421</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.058473588752204</v>
+        <v>-1.096008606157321</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.541384411031251</v>
+        <v>-2.635221954544045</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.61707844379936</v>
+        <v>1.560775917691684</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.42659580547397</v>
+        <v>-10.52043334898676</v>
       </c>
       <c r="E1880" t="n">
-        <v>-1.013713954591803</v>
+        <v>-1.05124897199692</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.467914579363803</v>
+        <v>-2.561752122876596</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.676532044293251</v>
+        <v>1.620229518185575</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.60172022286051</v>
+        <v>-10.69555776637331</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.069208500798903</v>
+        <v>-1.106743518204021</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.643038996750346</v>
+        <v>-2.73687654026314</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.586012614608841</v>
+        <v>1.529710088501165</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.836172316875</v>
+        <v>-10.93000986038779</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.170208503306295</v>
+        <v>-1.207743520711413</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.643038996750346</v>
+        <v>-2.73687654026314</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.578793449707245</v>
+        <v>1.522490923599569</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-11.12397616141224</v>
+        <v>-11.21781370492503</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.292002231895167</v>
+        <v>-1.329537249300284</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.930842841287585</v>
+        <v>-3.024680384800378</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.399438952210926</v>
+        <v>1.34313642610325</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-11.35380060857607</v>
+        <v>-11.44763815208886</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.382816220922141</v>
+        <v>-1.420351238327258</v>
       </c>
       <c r="F1884" t="n">
-        <v>-3.093490378357745</v>
+        <v>-3.187327921870539</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.302966219807386</v>
+        <v>1.24666369369971</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-11.58582952831233</v>
+        <v>-11.67966707182512</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.47293406018753</v>
+        <v>-1.510469077592648</v>
       </c>
       <c r="F1885" t="n">
-        <v>-3.155503075546168</v>
+        <v>-3.249340619058962</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.268452330123447</v>
+        <v>1.212149804015771</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-11.53381401434351</v>
+        <v>-11.62765155785631</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.448137518913605</v>
+        <v>-1.485672536318722</v>
       </c>
       <c r="F1886" t="n">
-        <v>-3.155503075546168</v>
+        <v>-3.249340619058962</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.272442665809848</v>
+        <v>1.216140139702172</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-11.67548585606763</v>
+        <v>-11.76932339958043</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.506281482501994</v>
+        <v>-1.543816499907112</v>
       </c>
       <c r="F1887" t="n">
-        <v>-3.155503075546168</v>
+        <v>-3.249340619058962</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.270967438911106</v>
+        <v>1.21466491280343</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-11.77439259652691</v>
+        <v>-11.8682301400397</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.530790768520833</v>
+        <v>-1.568325785925949</v>
       </c>
       <c r="F1888" t="n">
-        <v>-3.254409816005444</v>
+        <v>-3.348247359518238</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.226676804800413</v>
+        <v>1.170374278692737</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-11.57524048928981</v>
+        <v>-11.6690780328026</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.464181059272676</v>
+        <v>-1.501716076677793</v>
       </c>
       <c r="F1889" t="n">
-        <v>-3.089087290055631</v>
+        <v>-3.182924833568424</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.312819186723618</v>
+        <v>1.256516660615942</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-11.3493953365704</v>
+        <v>-11.44323288008319</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.364263925148702</v>
+        <v>-1.401798942553821</v>
       </c>
       <c r="F1890" t="n">
-        <v>-3.047160614468467</v>
+        <v>-3.140998157981261</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.347554265112125</v>
+        <v>1.291251739004449</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.0631205242477</v>
+        <v>-11.1569580677605</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.248614855663565</v>
+        <v>-1.286149873068684</v>
       </c>
       <c r="F1891" t="n">
-        <v>-3.047160614468467</v>
+        <v>-3.140998157981261</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.348693409668184</v>
+        <v>1.292390883560508</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.11601581229199</v>
+        <v>-11.20985335580479</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.267139196719173</v>
+        <v>-1.30467421412429</v>
       </c>
       <c r="F1892" t="n">
-        <v>-3.042205268380021</v>
+        <v>-3.136042811892815</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.354300391483359</v>
+        <v>1.297997865375683</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.83210708136324</v>
+        <v>-10.92594462487604</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.147842000109036</v>
+        <v>-1.185377017514154</v>
       </c>
       <c r="F1893" t="n">
-        <v>-3.042205268380021</v>
+        <v>-3.136042811892815</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.360034095721995</v>
+        <v>1.303731569614319</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.58511983117029</v>
+        <v>-10.67895737468309</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.058784362425721</v>
+        <v>-1.096319379830839</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.795218018187069</v>
+        <v>-2.889055561699863</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.498489183443901</v>
+        <v>1.442186657336225</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.32128296396622</v>
+        <v>-10.41512050747902</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.9631330968570011</v>
+        <v>-1.000668114262119</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.795218018187069</v>
+        <v>-2.889055561699863</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.488605702130994</v>
+        <v>1.432303176023318</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.05404116309782</v>
+        <v>-10.14787870661062</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.8580709370090154</v>
+        <v>-0.8956059544141328</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.795218018187069</v>
+        <v>-2.889055561699863</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.48677114163162</v>
+        <v>1.430468615523944</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.778231999697338</v>
+        <v>-9.872069543210133</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.7480475866222824</v>
+        <v>-0.7855826040273999</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.706198709908335</v>
+        <v>-2.800036253421129</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.5398824116254</v>
+        <v>1.483579885517723</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.75427845872138</v>
+        <v>-9.848116002234175</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.7377976640864055</v>
+        <v>-0.7753326814915233</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.682245168932378</v>
+        <v>-2.776082712445171</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.554923042356467</v>
+        <v>1.498620516248791</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.490218520398583</v>
+        <v>-9.584056063911378</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.6454340049190388</v>
+        <v>-0.6829690223241567</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.418185230609582</v>
+        <v>-2.512022774122376</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.700098689188393</v>
+        <v>1.643796163080717</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.783138896893746</v>
+        <v>-8.876976440406541</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.3653891891774048</v>
+        <v>-0.4029242065825227</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.418185230609582</v>
+        <v>-2.512022774122376</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.697311655528092</v>
+        <v>1.641009129420416</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.742954598527556</v>
+        <v>-8.83679214204035</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.3489718459430873</v>
+        <v>-0.3865068633482052</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.378000932243391</v>
+        <v>-2.471838475756185</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.721765858435648</v>
+        <v>1.665463332327972</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.48841269918648</v>
+        <v>-8.756722346502546</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.2477882649858998</v>
+        <v>-0.3551121239123263</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.123459032902316</v>
+        <v>-2.391768680218381</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.87385781926105</v>
+        <v>1.712872030871411</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.25493147695688</v>
+        <v>-8.523241124272946</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.1464713472562078</v>
+        <v>-0.2537952061826343</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.889977810672717</v>
+        <v>-2.158287457988782</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.021870981436662</v>
+        <v>1.860885193047023</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.075222946813007</v>
+        <v>-8.343532594129073</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.07748014551161742</v>
+        <v>-0.1848040044380439</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.832806306510021</v>
+        <v>-2.101115953826086</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.05328167362132</v>
+        <v>1.892295885231681</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-7.94294747318212</v>
+        <v>-8.211257120498185</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.02920246931223591</v>
+        <v>-0.136526328238662</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.700530832879134</v>
+        <v>-1.9688404801952</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.12801444454688</v>
+        <v>1.96702865615724</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.752347798508968</v>
+        <v>-8.020657445825032</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.04985246124466158</v>
+        <v>-0.05747139768176401</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.509931158205981</v>
+        <v>-1.778240805522047</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.245189310038408</v>
+        <v>2.084203521648768</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.503347999825387</v>
+        <v>-7.771657647141451</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.1623587219417528</v>
+        <v>0.05503486301532723</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.509931158205981</v>
+        <v>-1.778240805522047</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.258095651262066</v>
+        <v>2.097109862872427</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.608937989598491</v>
+        <v>-7.877247636914555</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.007853203566707379</v>
+        <v>-0.1151770624931334</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.615521147979086</v>
+        <v>-1.883830795295151</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.066765727798985</v>
+        <v>1.905779939409346</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.627672891717088</v>
+        <v>-7.895982539033152</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.03319717746293982</v>
+        <v>-0.07412668146348578</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.615521147979086</v>
+        <v>-1.883830795295151</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.115310069676072</v>
+        <v>1.954324281286432</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>3.088001770449517</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.350934717046275</v>
+        <v>-7.61924436436234</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.1472714593172597</v>
+        <v>0.03994760039083411</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.43370448686916</v>
+        <v>-1.702014134185225</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.227779078328022</v>
+        <v>2.066793289938382</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>3.079287784196039</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.224042310611205</v>
+        <v>-7.492351957927269</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.1893144356378098</v>
+        <v>0.08199057671138421</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.30681208043409</v>
+        <v>-1.575121727750155</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.295200535935586</v>
+        <v>2.134214747545946</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>3.072327172100946</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.036454802701279</v>
+        <v>-7.304764450017343</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.2573888267066873</v>
+        <v>0.1500649677802612</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.30681208043409</v>
+        <v>-1.575121727750155</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.288239923840492</v>
+        <v>2.127254135450853</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>3.086789526482089</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.794306409247421</v>
+        <v>-7.062616056563485</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.3687105384693736</v>
+        <v>0.2613866795429476</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.30681208043409</v>
+        <v>-1.575121727750155</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.302702278221636</v>
+        <v>2.141716489831996</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>3.081321646941284</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.731077037479072</v>
+        <v>-6.999386684795136</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.3885344076359076</v>
+        <v>0.281210548709482</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.30681208043409</v>
+        <v>-1.575121727750155</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.297234398680831</v>
+        <v>2.136248610291191</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>3.078819740951861</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.544589345102066</v>
+        <v>-6.81289899241813</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.4606275785972871</v>
+        <v>0.3533037196708615</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.120324388057084</v>
+        <v>-1.388634035373149</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.406625108117611</v>
+        <v>2.245639319727972</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>3.086520719189187</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.523440146198623</v>
+        <v>-6.791749793514687</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.4767882363959899</v>
+        <v>0.3694643774695643</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.09917518915364</v>
+        <v>-1.367484836469706</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.427015605697003</v>
+        <v>2.266029817307363</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>3.082301427536237</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.279674704215179</v>
+        <v>-6.547984351531243</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.5700751215364184</v>
+        <v>0.4627512626099928</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.09917518915364</v>
+        <v>-1.367484836469706</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.422796314044053</v>
+        <v>2.261810525654414</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>3.084425741456253</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.015646637021918</v>
+        <v>-6.283956284337982</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.6778106623337385</v>
+        <v>0.5704868034073129</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.8973097903376868</v>
+        <v>-1.165619437653752</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.546039867253642</v>
+        <v>2.385054078864002</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>3.077167816439955</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.765796243072844</v>
+        <v>-6.034105890388908</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.7704928948970706</v>
+        <v>0.663169035970645</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.8973097903376868</v>
+        <v>-1.165619437653752</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.538781942237343</v>
+        <v>2.377796153847704</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>3.080766939960604</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.462228754068865</v>
+        <v>-5.730538401384929</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.8955190140193108</v>
+        <v>0.7881951550928852</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.8973097903376868</v>
+        <v>-1.165619437653752</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.542381065757993</v>
+        <v>2.381395277368353</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>3.094094446015158</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.388748845216851</v>
+        <v>-5.657058492532915</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.9382384836146702</v>
+        <v>0.8309146246882446</v>
       </c>
       <c r="F1921" t="n">
-        <v>-0.8238298814856724</v>
+        <v>-1.092139528801738</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.599796517123755</v>
+        <v>2.438810728734115</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>3.093114923631455</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.163715845548028</v>
+        <v>-5.432025492864092</v>
       </c>
       <c r="E1922" t="n">
-        <v>1.027272161098496</v>
+        <v>0.9199483021720707</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.5987968818168495</v>
+        <v>-0.8671065291329151</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.733836794541345</v>
+        <v>2.572851006151706</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>3.097809724685772</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.949081467911621</v>
+        <v>-5.217391115227685</v>
       </c>
       <c r="E1923" t="n">
-        <v>1.117820713207376</v>
+        <v>1.010496854280951</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.3841625041804427</v>
+        <v>-0.6524721514965083</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.867312222177507</v>
+        <v>2.706326433787868</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>3.079003983469568</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.682481110937269</v>
+        <v>-4.950790758253333</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.205655114780913</v>
+        <v>1.098331255854487</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.3841625041804427</v>
+        <v>-0.6524721514965083</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.848506480961302</v>
+        <v>2.687520692571663</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>3.080747060094445</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.442050614132409</v>
+        <v>-4.710360261448473</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.303570390127734</v>
+        <v>1.196246531201309</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.1437320073755824</v>
+        <v>-0.412041654691648</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.994507855669096</v>
+        <v>2.833522067279457</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>3.084676373929265</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.199259806482964</v>
+        <v>-4.467569453799028</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.404616027022333</v>
+        <v>1.297292168095907</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.1437320073755824</v>
+        <v>-0.412041654691648</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.998437169503916</v>
+        <v>2.837451381114277</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>3.085354957846605</v>
       </c>
       <c r="D1927" t="n">
-        <v>-3.959654714875874</v>
+        <v>-4.227964362191939</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.501136647582508</v>
+        <v>1.393812788656082</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.07668405970708791</v>
+        <v>-0.3449937070231535</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.039344522022353</v>
+        <v>2.878358733632714</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>3.082353029066599</v>
       </c>
       <c r="D1928" t="n">
-        <v>-3.716999126452711</v>
+        <v>-3.985308773768776</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.595196954171767</v>
+        <v>1.487873095245341</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.07668405970708791</v>
+        <v>-0.3449937070231535</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.036342593242346</v>
+        <v>2.875356804852707</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>3.083932066077213</v>
       </c>
       <c r="D1929" t="n">
-        <v>-3.4969783284157</v>
+        <v>-3.765287975731765</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.684784310397186</v>
+        <v>1.57746045147076</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.06453578536089233</v>
+        <v>-0.2037738619551732</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.122653537293749</v>
+        <v>2.961667748904109</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.851952635846496</v>
+        <v>3.56768974600297</v>
       </c>
       <c r="C1930" t="n">
         <v>3.099826248879036</v>
       </c>
       <c r="D1930" t="n">
-        <v>-3.556303768047496</v>
+        <v>-3.563214665616503</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.67694831734629</v>
+        <v>1.674183958318688</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.06453578536089233</v>
+        <v>-0.2037738619551732</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.138547720095572</v>
+        <v>2.977561931705933</v>
       </c>
     </row>
   </sheetData>
